--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>6.17</v>
+        <v>5.75</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>5.33</v>
+        <v>5.12</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>5.83</v>
+        <v>5.12</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>5.62</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1931,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2275,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.17</v>
+        <v>3.75</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3004,10 +3004,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6131,10 +6131,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -6218,10 +6218,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>6.5</v>
+        <v>6.12</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -6305,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -6453,10 +6453,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -6540,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>5.67</v>
+        <v>5.88</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -6975,10 +6975,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -7062,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7408,13 +7408,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>5.5</v>
+        <v>6.12</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -7928,13 +7928,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -8187,10 +8187,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -8274,10 +8274,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -8361,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>6.5</v>
+        <v>6.12</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
         <v>6</v>
@@ -9926,10 +9926,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -10274,10 +10274,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -10359,10 +10359,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10707,10 +10707,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -10794,10 +10794,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T60" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -10968,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T62" t="n">
         <v>6</v>
@@ -11142,10 +11142,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -11227,10 +11227,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -11314,10 +11314,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T66" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -11399,10 +11399,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>5.17</v>
+        <v>5.5</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -11741,10 +11741,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>5.83</v>
+        <v>6.12</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -11891,10 +11891,10 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>7.67</v>
+        <v>7.12</v>
       </c>
       <c r="U73" t="n">
         <v>1</v>
@@ -12074,10 +12074,10 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -12135,13 +12135,13 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T77" t="n">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" t="n">
         <v>2</v>
@@ -12257,10 +12257,10 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T79" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -12440,10 +12440,10 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -12501,10 +12501,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -12852,16 +12852,16 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T88" t="n">
-        <v>5.83</v>
+        <v>6.12</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" t="n">
         <v>2</v>
@@ -13461,10 +13461,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T95" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -13548,10 +13548,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -13722,7 +13722,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T98" t="n">
         <v>5.5</v>
@@ -14155,10 +14155,10 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T104" t="n">
-        <v>6.17</v>
+        <v>5.75</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -14501,10 +14501,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T107" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -14932,10 +14932,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T112" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -15019,10 +15019,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T113" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="U113" t="n">
         <v>1</v>
@@ -15189,10 +15189,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -15361,10 +15361,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T117" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -15881,16 +15881,16 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T123" t="n">
-        <v>5.83</v>
+        <v>6.12</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W123" t="n">
         <v>9</v>
@@ -15966,10 +15966,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T124" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -16138,10 +16138,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T126" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -16393,10 +16393,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -16691,10 +16691,10 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T133" t="n">
-        <v>6.5</v>
+        <v>6.38</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -17179,16 +17179,16 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -18594,10 +18594,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T158" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -19752,10 +19752,10 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T172" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="U172" t="n">
         <v>0</v>
@@ -20240,10 +20240,10 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T180" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -21412,16 +21412,16 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -21760,7 +21760,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>7.5</v>
@@ -21769,7 +21769,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
         <v>4</v>
@@ -21930,10 +21930,10 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -22017,10 +22017,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>10.17</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="U10" t="n">
         <v>3</v>
@@ -22278,10 +22278,10 @@
         <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
@@ -22452,10 +22452,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>8.5</v>
+        <v>7.83</v>
       </c>
       <c r="U15" t="n">
         <v>1</v>
@@ -22626,10 +22626,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>6.83</v>
+        <v>6.5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -22974,10 +22974,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>6.67</v>
+        <v>6.38</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -23059,10 +23059,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -23231,7 +23231,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
         <v>5.5</v>
@@ -23405,10 +23405,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>7.17</v>
+        <v>6.75</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
         <v>6</v>
@@ -23664,16 +23664,16 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
         <v>6</v>
@@ -23751,10 +23751,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -23923,10 +23923,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>8.33</v>
+        <v>7.62</v>
       </c>
       <c r="U32" t="n">
         <v>2</v>
@@ -24110,10 +24110,10 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -24232,10 +24232,10 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -24354,13 +24354,13 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -24953,10 +24953,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -25038,10 +25038,10 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -25473,10 +25473,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -25560,10 +25560,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -26169,10 +26169,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -26256,13 +26256,13 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>5.67</v>
+        <v>6.75</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -26776,10 +26776,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>8.75</v>
+        <v>7.67</v>
       </c>
       <c r="U67" t="n">
         <v>1</v>
@@ -26950,10 +26950,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -27035,10 +27035,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T70" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="U70" t="n">
         <v>1</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -27209,10 +27209,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -27296,10 +27296,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -27383,13 +27383,13 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>6.33</v>
+        <v>7.38</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -27470,10 +27470,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -27881,10 +27881,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T80" t="n">
-        <v>7.5</v>
+        <v>7.38</v>
       </c>
       <c r="U80" t="n">
         <v>1</v>
@@ -27942,10 +27942,10 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -28003,16 +28003,16 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -28125,7 +28125,7 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
         <v>5.5</v>
@@ -28186,10 +28186,10 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T88" t="n">
         <v>5.5</v>
@@ -28565,10 +28565,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>6.83</v>
+        <v>6.5</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
@@ -28998,10 +28998,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -29085,13 +29085,13 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T96" t="n">
-        <v>7.67</v>
+        <v>8.25</v>
       </c>
       <c r="U96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V96" t="n">
         <v>1</v>
@@ -29172,13 +29172,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" t="n">
-        <v>6.33</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V97" t="n">
         <v>1</v>
@@ -29259,7 +29259,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T98" t="n">
         <v>6</v>
@@ -29433,7 +29433,7 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T100" t="n">
         <v>6</v>
@@ -29520,10 +29520,10 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T101" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -29781,10 +29781,10 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T104" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -30040,10 +30040,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T107" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -30212,10 +30212,10 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T109" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -30384,16 +30384,16 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T111" t="n">
-        <v>6.17</v>
+        <v>6.75</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" t="n">
         <v>6</v>
@@ -30558,16 +30558,16 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T113" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W113" t="n">
         <v>4</v>
@@ -31335,10 +31335,10 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -31420,16 +31420,16 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T123" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
@@ -31505,10 +31505,10 @@
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -31762,13 +31762,13 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T127" t="n">
-        <v>6</v>
+        <v>9.75</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -31849,10 +31849,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T128" t="n">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -31934,10 +31934,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -32189,10 +32189,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -32426,10 +32426,10 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T135" t="n">
-        <v>5.83</v>
+        <v>6.12</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -32487,16 +32487,16 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T136" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
@@ -32792,10 +32792,10 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -33293,10 +33293,10 @@
         <v>1</v>
       </c>
       <c r="S148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T148" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -33987,10 +33987,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T159" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -34335,10 +34335,10 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T160" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
@@ -34509,16 +34509,16 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T162" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
       </c>
       <c r="V162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W162" t="n">
         <v>2</v>
@@ -34768,10 +34768,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T165" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -34942,7 +34942,7 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T167" t="n">
         <v>6</v>
@@ -35029,10 +35029,10 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T168" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -35543,10 +35543,10 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T174" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -35713,7 +35713,7 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T176" t="n">
         <v>6</v>
@@ -36911,10 +36911,10 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U194" t="n">
         <v>0</v>
@@ -37347,10 +37347,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -37497,10 +37497,10 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -37580,10 +37580,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>6.67</v>
+        <v>6.38</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -37754,13 +37754,13 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>5.83</v>
+        <v>6.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -37841,10 +37841,10 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>8.25</v>
+        <v>7.33</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -38100,16 +38100,16 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
         <v>4</v>
@@ -38272,16 +38272,16 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -38533,10 +38533,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -38598,10 +38598,10 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -38681,13 +38681,13 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -38855,10 +38855,10 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -39203,10 +39203,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>7.75</v>
+        <v>7.17</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -39464,10 +39464,10 @@
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -39636,10 +39636,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>6.83</v>
+        <v>6.5</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -39808,13 +39808,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -40152,10 +40152,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>10.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="U37" t="n">
         <v>4</v>
@@ -40400,10 +40400,10 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
@@ -40461,10 +40461,10 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
       <c r="U42" t="n">
         <v>2</v>
@@ -40890,13 +40890,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -40977,10 +40977,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -41149,10 +41149,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -41323,13 +41323,13 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>7.17</v>
+        <v>7.88</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -41408,10 +41408,10 @@
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -41495,7 +41495,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
         <v>6</v>
@@ -41580,13 +41580,13 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -41665,10 +41665,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -41839,10 +41839,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -42011,10 +42011,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -42096,13 +42096,13 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>8.17</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
         <v>1</v>
@@ -42222,10 +42222,10 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -42405,10 +42405,10 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="U66" t="n">
         <v>1</v>
@@ -42466,13 +42466,13 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -43420,10 +43420,10 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>57</v>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>52</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>83</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>68</v>
@@ -965,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>5.17</v>
+        <v>4.38</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>28</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1848,10 +1848,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
@@ -2362,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
         <v>250</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>47</v>
@@ -6370,7 +6370,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>6</v>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>47</v>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>35</v>
@@ -6627,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>36</v>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>26</v>
@@ -7149,10 +7149,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7234,10 +7234,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7345,27 +7345,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Carlos Augusto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>76.7</v>
+        <v>80.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7381,46 +7381,46 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="L20" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.04</v>
+        <v>-0.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>6.12</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -7432,27 +7432,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Miranda J.</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>75.3</v>
+        <v>76.7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -7468,46 +7468,46 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="L21" t="n">
-        <v>6.1</v>
+        <v>6.14</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0.789</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>6.33</v>
+        <v>6.12</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -7519,27 +7519,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Delprato</t>
+          <t>Miranda J.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B;Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>72</v>
+        <v>75.3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7555,28 +7555,28 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>6.01</v>
+        <v>6.1</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="O22" t="n">
-        <v>0.908</v>
+        <v>0.789</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -7585,16 +7585,16 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>5.83</v>
+        <v>6.33</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -7606,56 +7606,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ramon</t>
+          <t>Delprato</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="n">
-        <v>31</v>
-      </c>
-      <c r="F23" t="n">
-        <v>16</v>
-      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
           <t>1a Fascia</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>70.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>6.16</v>
+        <v>5.91</v>
       </c>
       <c r="L23" t="n">
-        <v>6.14</v>
+        <v>6.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="O23" t="n">
-        <v>0.842</v>
+        <v>0.908</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -7667,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -7679,10 +7681,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
@@ -7691,85 +7693,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Valeri</t>
+          <t>Ramon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>32</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
         <v>11</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>34</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2</v>
-      </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -7778,27 +7778,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dodò</t>
+          <t>Valeri</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7814,25 +7814,25 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="L25" t="n">
-        <v>6.03</v>
+        <v>6.09</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0.675</v>
+        <v>0.728</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
@@ -7841,10 +7841,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>6.12</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -7853,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -7865,21 +7865,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tiago Gabriel</t>
+          <t>Dodò</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -7904,37 +7904,37 @@
         <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="L26" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.24</v>
+        <v>-0.01</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5</v>
+        <v>0.675</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
         <v>5.5</v>
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
@@ -8511,10 +8511,10 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -8633,10 +8633,10 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
         <v>13</v>
@@ -8803,10 +8803,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -9001,21 +9001,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carlos Augusto</t>
+          <t>Dragusin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
         <v>20</v>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>80.8</v>
+        <v>79.8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9037,25 +9037,23 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="L40" t="n">
-        <v>6.16</v>
+        <v>6.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>0.798</v>
+        <v>0.5</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -9064,10 +9062,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>7.5</v>
+        <v>5.12</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -9076,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -9088,27 +9086,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dragusin</t>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -9116,49 +9114,49 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>79.8</v>
+        <v>76.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>6.11</v>
+        <v>6.06</v>
       </c>
       <c r="L41" t="n">
-        <v>6.45</v>
+        <v>6.41</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>0.5</v>
+        <v>0.421</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>5.12</v>
+        <v>6</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
@@ -9173,17 +9171,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Obrador</t>
+          <t>Monterisi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -9201,7 +9199,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>76.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9209,35 +9207,35 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>6.06</v>
+        <v>5.83</v>
       </c>
       <c r="L42" t="n">
-        <v>6.41</v>
+        <v>6.25</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>0.421</v>
+        <v>0.474</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -9258,27 +9256,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Monterisi</t>
+          <t>Vojvoda</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -9286,43 +9284,45 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>75.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>5.83</v>
+        <v>6.02</v>
       </c>
       <c r="L43" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.23</v>
+      </c>
       <c r="O43" t="n">
-        <v>0.474</v>
+        <v>0.658</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -9331,7 +9331,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -9343,73 +9343,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vojvoda</t>
+          <t>Rensch</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
+        <v>14</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
         <v>19</v>
       </c>
-      <c r="F44" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>27</v>
-      </c>
       <c r="K44" t="n">
-        <v>6.02</v>
+        <v>6.16</v>
       </c>
       <c r="L44" t="n">
-        <v>6.24</v>
+        <v>6.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="O44" t="n">
-        <v>0.658</v>
+        <v>0.355</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -9430,27 +9430,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rensch</t>
+          <t>Holm</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B;Dd;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -9458,30 +9458,30 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>73.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>6.16</v>
+        <v>6.09</v>
       </c>
       <c r="L45" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="O45" t="n">
-        <v>0.355</v>
+        <v>0.439</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -9493,10 +9493,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Holm</t>
+          <t>Belghali</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9527,75 +9527,73 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>26</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>6</v>
       </c>
-      <c r="E46" t="n">
-        <v>13</v>
-      </c>
-      <c r="F46" t="n">
-        <v>6</v>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>16</v>
-      </c>
-      <c r="K46" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="L46" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>6</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -9604,27 +9602,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Belghali</t>
+          <t>Mina</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -9643,44 +9641,46 @@
         <v>26</v>
       </c>
       <c r="K47" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>6.21</v>
+        <v>6.17</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.03</v>
+      </c>
       <c r="O47" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -9689,21 +9689,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mina</t>
+          <t>Marusic</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
         <v>20</v>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>72.2</v>
+        <v>71</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -9725,38 +9725,38 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K48" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>6</v>
       </c>
-      <c r="L48" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
         <v>1</v>
@@ -9776,27 +9776,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marusic</t>
+          <t>Celik</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>B;Dd;E</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>71</v>
+        <v>68.3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -9812,22 +9812,22 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K49" t="n">
-        <v>5.86</v>
+        <v>6.17</v>
       </c>
       <c r="L49" t="n">
-        <v>5.97</v>
+        <v>6.27</v>
       </c>
       <c r="M49" t="n">
         <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.03</v>
+        <v>0.46</v>
       </c>
       <c r="O49" t="n">
-        <v>0.886</v>
+        <v>0.649</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -9839,10 +9839,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>5.62</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -9851,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X49" t="n">
         <v>1</v>
@@ -9863,24 +9863,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Celik</t>
+          <t>Buongiorno</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B;Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
         <v>8</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>68.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -9902,34 +9902,34 @@
         <v>32</v>
       </c>
       <c r="K50" t="n">
-        <v>6.17</v>
+        <v>5.89</v>
       </c>
       <c r="L50" t="n">
-        <v>6.27</v>
+        <v>5.88</v>
       </c>
       <c r="M50" t="n">
         <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>0.46</v>
+        <v>-0.59</v>
       </c>
       <c r="O50" t="n">
-        <v>0.649</v>
+        <v>0.728</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -9938,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Buongiorno</t>
+          <t>Tiago Gabriel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9960,72 +9960,72 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>68</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>36</v>
+      </c>
+      <c r="K51" t="n">
         <v>6</v>
       </c>
-      <c r="E51" t="n">
-        <v>15</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>32</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5.89</v>
-      </c>
       <c r="L51" t="n">
-        <v>5.88</v>
+        <v>6.01</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.59</v>
+        <v>-0.24</v>
       </c>
       <c r="O51" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
         <v>18</v>
@@ -10446,10 +10446,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
         <v>14</v>
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>13</v>
@@ -11055,10 +11055,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T63" t="n">
-        <v>7.17</v>
+        <v>6.75</v>
       </c>
       <c r="U63" t="n">
         <v>1</v>
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
         <v>15</v>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
         <v>17</v>
@@ -11656,10 +11656,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T70" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
         <v>13</v>
@@ -11850,24 +11850,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bracaglia</t>
+          <t>Mangas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
@@ -11894,13 +11894,13 @@
         <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>7.12</v>
+        <v>7.5</v>
       </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
@@ -11911,27 +11911,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Doekhi</t>
+          <t>Kaiki</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
@@ -11952,16 +11952,16 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>6.67</v>
+        <v>9.5</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Koulierakis</t>
+          <t>Doekhi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -11982,14 +11982,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
@@ -12013,16 +12013,16 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -12094,24 +12094,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mangas</t>
+          <t>Bracaglia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F77" t="n">
         <v>8</v>
@@ -12138,13 +12138,13 @@
         <v>4</v>
       </c>
       <c r="T77" t="n">
-        <v>7.5</v>
+        <v>7.12</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -12155,27 +12155,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kaiki</t>
+          <t>Koulierakis</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -12196,10 +12196,10 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -12277,27 +12277,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Badiashile</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -12338,7 +12338,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Badiashile</t>
+          <t>Sutalo J.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12348,17 +12348,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>6</v>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -12399,27 +12399,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sutalo J.</t>
+          <t>Sugawara</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -12460,27 +12460,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sugawara</t>
+          <t>Leite</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -12501,10 +12501,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -12521,27 +12521,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Leite</t>
+          <t>Valdepenas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>13</v>
+      </c>
+      <c r="F84" t="n">
         <v>6</v>
-      </c>
-      <c r="E84" t="n">
-        <v>14</v>
-      </c>
-      <c r="F84" t="n">
-        <v>7</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -12562,10 +12562,10 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -12582,27 +12582,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Valdepenas</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>2</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -12684,10 +12684,10 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T86" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -12765,10 +12765,10 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
         <v>12</v>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
         <v>12</v>
@@ -13026,10 +13026,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T90" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
         <v>12</v>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
         <v>12</v>
@@ -13374,10 +13374,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>8.83</v>
+        <v>7.88</v>
       </c>
       <c r="U94" t="n">
         <v>2</v>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
         <v>12</v>
@@ -13760,7 +13760,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
         <v>12</v>
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
         <v>10</v>
@@ -14106,7 +14106,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
         <v>12</v>
@@ -14327,10 +14327,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T105" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E111" t="n">
         <v>12</v>
@@ -14847,10 +14847,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T111" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -14885,7 +14885,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E112" t="n">
         <v>12</v>
@@ -15104,7 +15104,7 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T114" t="n">
         <v>6</v>
@@ -15399,7 +15399,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E122" t="n">
         <v>12</v>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E123" t="n">
         <v>12</v>
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>10</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E131" t="n">
         <v>10</v>
@@ -16565,13 +16565,13 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T131" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -16589,27 +16589,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kofler</t>
+          <t>Leysen F.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>12</v>
+      </c>
+      <c r="F132" t="n">
         <v>6</v>
-      </c>
-      <c r="E132" t="n">
-        <v>8</v>
-      </c>
-      <c r="F132" t="n">
-        <v>4</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -16630,16 +16630,16 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
@@ -16650,24 +16650,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Leysen F.</t>
+          <t>Balerdi</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F133" t="n">
         <v>6</v>
@@ -16691,16 +16691,16 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T133" t="n">
-        <v>6.38</v>
+        <v>6.75</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
@@ -16711,24 +16711,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Balerdi</t>
+          <t>Viery</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>6</v>
       </c>
       <c r="E134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F134" t="n">
         <v>6</v>
@@ -16752,10 +16752,10 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T134" t="n">
-        <v>6.5</v>
+        <v>5.67</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -16833,27 +16833,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Viery</t>
+          <t>Kofler</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>5</v>
       </c>
       <c r="E136" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -16874,10 +16874,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T136" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -16955,24 +16955,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Favasuli</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>5</v>
       </c>
       <c r="E138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F138" t="n">
         <v>6</v>
@@ -16999,13 +16999,13 @@
         <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
@@ -17016,27 +17016,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E139" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -17057,10 +17057,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -17077,17 +17077,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -17118,10 +17118,10 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -17138,27 +17138,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Favasuli</t>
+          <t>Lulli</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -17179,16 +17179,16 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T141" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -17199,17 +17199,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lulli</t>
+          <t>Drameh</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -17240,10 +17240,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -17260,21 +17260,21 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Drameh</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
         <v>10</v>
@@ -17301,10 +17301,10 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -18163,10 +18163,10 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T153" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -19772,27 +19772,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Tchato</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
@@ -19813,10 +19813,10 @@
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19833,27 +19833,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
@@ -19894,27 +19894,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
@@ -19955,27 +19955,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
@@ -19996,10 +19996,10 @@
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20016,24 +20016,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Tchato</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D177" t="n">
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -20057,10 +20057,10 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T177" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U177" t="n">
         <v>0</v>
@@ -20077,27 +20077,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
@@ -20138,24 +20138,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D179" t="n">
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F179" t="n">
         <v>2</v>
@@ -20199,17 +20199,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -20240,10 +20240,10 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T180" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -21325,16 +21325,16 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>7.17</v>
+        <v>7.25</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>5</v>
@@ -21363,7 +21363,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
         <v>140</v>
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
         <v>242</v>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>152</v>
@@ -21711,7 +21711,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
         <v>142</v>
@@ -21798,7 +21798,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>155</v>
@@ -21845,10 +21845,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>8.5</v>
+        <v>7.88</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -22104,10 +22104,10 @@
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -22142,7 +22142,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>65</v>
@@ -22191,10 +22191,10 @@
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -22316,7 +22316,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
         <v>81</v>
@@ -22365,13 +22365,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
@@ -22539,10 +22539,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>57</v>
@@ -22887,13 +22887,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>7.83</v>
+        <v>8.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
@@ -23097,7 +23097,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
         <v>42</v>
@@ -23146,16 +23146,16 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>7.67</v>
+        <v>7.75</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
         <v>3</v>
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>72</v>
@@ -23356,7 +23356,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
         <v>50</v>
@@ -23577,10 +23577,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
         <v>43</v>
@@ -23836,7 +23836,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
         <v>7.5</v>
@@ -23845,7 +23845,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
@@ -23874,7 +23874,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
         <v>40</v>
@@ -23988,10 +23988,10 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>7.5</v>
+        <v>7.12</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -24008,27 +24008,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jones C.</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -24049,13 +24049,13 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -24069,27 +24069,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kessiè</t>
+          <t>Moreira</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F35" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -24110,13 +24110,13 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -24130,27 +24130,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goncalves P.</t>
+          <t>Jones C.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -24171,10 +24171,10 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -24252,27 +24252,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Kessiè</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -24293,13 +24293,13 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>8.380000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -24313,27 +24313,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Moreira</t>
+          <t>Goncalves P.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E;W</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -24354,13 +24354,13 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -24388,7 +24388,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>32</v>
@@ -24609,10 +24609,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -24647,7 +24647,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
         <v>22</v>
@@ -25647,10 +25647,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T55" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -25946,7 +25946,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
         <v>19</v>
@@ -25995,13 +25995,13 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T58" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -26207,7 +26207,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
         <v>21</v>
@@ -26294,7 +26294,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
         <v>20</v>
@@ -26466,7 +26466,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
         <v>22</v>
@@ -26553,7 +26553,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
         <v>18</v>
@@ -26640,7 +26640,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
         <v>25</v>
@@ -27334,7 +27334,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E74" t="n">
         <v>23</v>
@@ -27421,7 +27421,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
         <v>28</v>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
         <v>18</v>
@@ -27644,10 +27644,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T77" t="n">
-        <v>7.5</v>
+        <v>6.88</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
@@ -27769,7 +27769,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E79" t="n">
         <v>28</v>
@@ -27816,10 +27816,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T79" t="n">
-        <v>6.5</v>
+        <v>6.38</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -27840,7 +27840,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Romano</t>
+          <t>Calò</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -27850,17 +27850,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -27884,13 +27884,13 @@
         <v>4</v>
       </c>
       <c r="T80" t="n">
-        <v>7.38</v>
+        <v>6.62</v>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
@@ -27901,7 +27901,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Calò</t>
+          <t>Romano</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -27911,17 +27911,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F81" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -27945,13 +27945,13 @@
         <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>6.62</v>
+        <v>7.38</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -28037,7 +28037,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" t="n">
         <v>21</v>
@@ -28206,27 +28206,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Milla</t>
+          <t>Braganca</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -28267,27 +28267,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Braganca</t>
+          <t>Milla</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -28308,10 +28308,10 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -28342,7 +28342,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
         <v>15</v>
@@ -28429,7 +28429,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
         <v>12</v>
@@ -28478,10 +28478,10 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T89" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
         <v>11</v>
@@ -28850,27 +28850,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Addai</t>
+          <t>Loftus-Cheek</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>4</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -28878,43 +28878,45 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>60.4</v>
+        <v>57.8</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K94" t="n">
-        <v>5.96</v>
+        <v>6.1</v>
       </c>
       <c r="L94" t="n">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O94" t="n">
-        <v>0.316</v>
+        <v>0.596</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -28923,7 +28925,7 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
@@ -28935,27 +28937,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Loftus-Cheek</t>
+          <t>De Roon</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>4</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -28963,45 +28965,45 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>57.8</v>
+        <v>57.2</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K95" t="n">
-        <v>6.1</v>
+        <v>5.97</v>
       </c>
       <c r="L95" t="n">
-        <v>6.52</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
         <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="O95" t="n">
-        <v>0.596</v>
+        <v>0.877</v>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>5.62</v>
+        <v>6.5</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -29010,10 +29012,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -29036,7 +29038,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E96" t="n">
         <v>16</v>
@@ -29123,7 +29125,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E97" t="n">
         <v>17</v>
@@ -29210,7 +29212,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
         <v>12</v>
@@ -29384,7 +29386,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" t="n">
         <v>12</v>
@@ -29471,7 +29473,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
         <v>12</v>
@@ -29819,7 +29821,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E105" t="n">
         <v>12</v>
@@ -30078,7 +30080,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E108" t="n">
         <v>14</v>
@@ -30250,7 +30252,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
         <v>15</v>
@@ -30335,7 +30337,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E111" t="n">
         <v>15</v>
@@ -30509,7 +30511,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E113" t="n">
         <v>13</v>
@@ -30596,7 +30598,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E114" t="n">
         <v>15</v>
@@ -30645,10 +30647,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T114" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -30855,7 +30857,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E117" t="n">
         <v>11</v>
@@ -30904,16 +30906,16 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T117" t="n">
-        <v>5.5</v>
+        <v>6.17</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
@@ -30942,7 +30944,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E118" t="n">
         <v>12</v>
@@ -30991,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T118" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -31163,10 +31165,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T120" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -31286,7 +31288,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E122" t="n">
         <v>16</v>
@@ -31543,7 +31545,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" t="n">
         <v>16</v>
@@ -31715,7 +31717,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E127" t="n">
         <v>14</v>
@@ -32446,17 +32448,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Unai Gomez</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -32487,10 +32489,10 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T136" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -32507,7 +32509,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Oulai</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -32517,17 +32519,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E137" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F137" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
@@ -32548,16 +32550,16 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="n">
-        <v>5.67</v>
+        <v>5.88</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
@@ -32568,7 +32570,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fitz-Jim</t>
+          <t>Oulai</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -32578,7 +32580,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -32612,7 +32614,7 @@
         <v>3</v>
       </c>
       <c r="T138" t="n">
-        <v>6.17</v>
+        <v>5.67</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -32629,27 +32631,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Unai Gomez</t>
+          <t>Fitz-Jim</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>6</v>
       </c>
       <c r="E139" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F139" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -32670,10 +32672,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T139" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -32690,27 +32692,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Meichtry</t>
+          <t>Amondarain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>10</v>
+      </c>
+      <c r="F140" t="n">
         <v>5</v>
-      </c>
-      <c r="E140" t="n">
-        <v>11</v>
-      </c>
-      <c r="F140" t="n">
-        <v>6</v>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
@@ -32734,7 +32736,7 @@
         <v>2</v>
       </c>
       <c r="T140" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -32751,7 +32753,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Amondarain</t>
+          <t>Cichella</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -32761,17 +32763,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>4</v>
       </c>
       <c r="E141" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -32795,7 +32797,7 @@
         <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -32812,24 +32814,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cichella</t>
+          <t>Meichtry</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F142" t="n">
         <v>6</v>
@@ -32856,7 +32858,7 @@
         <v>2</v>
       </c>
       <c r="T142" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -33119,10 +33121,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -33230,82 +33232,80 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Messias</t>
+          <t>Addai</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D148" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>10</v>
+      </c>
+      <c r="F148" t="n">
         <v>5</v>
       </c>
-      <c r="E148" t="n">
-        <v>8</v>
-      </c>
-      <c r="F148" t="n">
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>12</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L148" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="P148" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
         <v>4</v>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
-        <v>19</v>
-      </c>
-      <c r="K148" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="L148" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="M148" t="n">
-        <v>3</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="P148" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>1</v>
-      </c>
-      <c r="R148" t="n">
-        <v>1</v>
-      </c>
-      <c r="S148" t="n">
-        <v>4</v>
-      </c>
-      <c r="T148" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" t="n">
-        <v>1</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -33317,35 +33317,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Gandelman</t>
+          <t>Messias</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D149" t="n">
+        <v>5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>8</v>
+      </c>
+      <c r="F149" t="n">
         <v>4</v>
       </c>
-      <c r="E149" t="n">
-        <v>10</v>
-      </c>
-      <c r="F149" t="n">
-        <v>5</v>
-      </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>57.2</v>
+        <v>59.3</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -33353,35 +33353,37 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K149" t="n">
-        <v>5.97</v>
+        <v>6.18</v>
       </c>
       <c r="L149" t="n">
-        <v>6.41</v>
+        <v>6.68</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
-      </c>
-      <c r="N149" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.53</v>
+      </c>
       <c r="O149" t="n">
-        <v>0.421</v>
+        <v>0.456</v>
       </c>
       <c r="P149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q149" t="n">
         <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -33390,7 +33392,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -33402,21 +33404,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>De Roon</t>
+          <t>Gandelman</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E150" t="n">
         <v>10</v>
@@ -33438,28 +33440,26 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K150" t="n">
         <v>5.97</v>
       </c>
       <c r="L150" t="n">
-        <v>6</v>
+        <v>6.41</v>
       </c>
       <c r="M150" t="n">
-        <v>3</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-0.32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="n">
-        <v>0.877</v>
+        <v>0.421</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -33477,10 +33477,10 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
@@ -33503,7 +33503,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
         <v>8</v>
@@ -33900,7 +33900,7 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T155" t="n">
         <v>5.5</v>
@@ -33938,7 +33938,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
         <v>10</v>
@@ -34199,7 +34199,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E159" t="n">
         <v>8</v>
@@ -34460,7 +34460,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E162" t="n">
         <v>10</v>
@@ -34893,7 +34893,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" t="n">
         <v>5</v>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E168" t="n">
         <v>7</v>
@@ -35666,7 +35666,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E176" t="n">
         <v>5</v>
@@ -35897,7 +35897,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
         <v>8</v>
@@ -36066,27 +36066,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Foe Ondoa</t>
+          <t>Chakvetadze</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
@@ -36127,27 +36127,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Jovanovic</t>
+          <t>Foe Ondoa</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D183" t="n">
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
@@ -36168,10 +36168,10 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U183" t="n">
         <v>0</v>
@@ -36188,7 +36188,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Chakvetadze</t>
+          <t>Jovanovic</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -36202,13 +36202,13 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>El Azzouzi A.</t>
+          <t>Sierro</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -36514,11 +36514,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -36545,10 +36545,10 @@
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -36565,17 +36565,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Dagasso</t>
+          <t>El Azzouzi A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -36606,10 +36606,10 @@
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
@@ -36626,17 +36626,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Laerke</t>
+          <t>Dagasso</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -36667,10 +36667,10 @@
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U190" t="n">
         <v>0</v>
@@ -36687,17 +36687,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Comotto</t>
+          <t>Laerke</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -36748,17 +36748,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ciervo</t>
+          <t>Comotto</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -36809,17 +36809,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sierro</t>
+          <t>Ciervo</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -37126,7 +37126,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
         <v>390</v>
@@ -37213,7 +37213,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
         <v>260</v>
@@ -37262,16 +37262,16 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
@@ -37300,7 +37300,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
         <v>285</v>
@@ -37432,13 +37432,13 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>12.33</v>
+        <v>11.75</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -37470,7 +37470,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
         <v>232</v>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>96</v>
@@ -37705,7 +37705,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -37792,7 +37792,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>108</v>
@@ -37928,10 +37928,10 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>8.33</v>
+        <v>7.75</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>105</v>
@@ -38013,13 +38013,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -38051,7 +38051,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
         <v>80</v>
@@ -38138,7 +38138,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
         <v>185</v>
@@ -38187,10 +38187,10 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -38359,10 +38359,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>8.67</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -38446,7 +38446,7 @@
         <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>7</v>
@@ -38455,7 +38455,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
         <v>5</v>
@@ -38484,7 +38484,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
         <v>92</v>
@@ -38571,7 +38571,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
         <v>140</v>
@@ -38632,7 +38632,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>35</v>
@@ -38768,10 +38768,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>9.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -38806,7 +38806,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>52</v>
@@ -38893,7 +38893,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
         <v>31</v>
@@ -39116,10 +39116,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -39241,7 +39241,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
         <v>50</v>
@@ -39377,10 +39377,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -39415,7 +39415,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
         <v>55</v>
@@ -39723,10 +39723,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>9</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="U32" t="n">
         <v>2</v>
@@ -39761,7 +39761,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -39931,7 +39931,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -39980,10 +39980,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -40176,7 +40176,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kevin Carlos</t>
+          <t>Adams A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -40186,17 +40186,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
@@ -40217,13 +40217,13 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -40237,7 +40237,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Adams A.</t>
+          <t>Kevin Carlos</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -40247,17 +40247,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
@@ -40278,13 +40278,13 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -40312,7 +40312,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
         <v>32</v>
@@ -40339,13 +40339,13 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>6</v>
+        <v>7.33</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -40495,7 +40495,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
         <v>15</v>
@@ -40544,13 +40544,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -40716,10 +40716,10 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -40841,7 +40841,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
         <v>8</v>
@@ -40928,7 +40928,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
         <v>12</v>
@@ -41062,7 +41062,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
         <v>5.5</v>
@@ -41274,7 +41274,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
         <v>25</v>
@@ -41361,7 +41361,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
         <v>11</v>
@@ -41533,7 +41533,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
         <v>14</v>
@@ -41618,7 +41618,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
         <v>14</v>
@@ -42049,7 +42049,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
         <v>30</v>
@@ -42120,7 +42120,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Geubbels</t>
+          <t>Bobcek</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -42130,17 +42130,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D62" t="n">
+        <v>9</v>
+      </c>
+      <c r="E62" t="n">
+        <v>15</v>
+      </c>
+      <c r="F62" t="n">
         <v>8</v>
-      </c>
-      <c r="E62" t="n">
-        <v>21</v>
-      </c>
-      <c r="F62" t="n">
-        <v>10</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
@@ -42161,10 +42161,10 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -42181,7 +42181,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bobcek</t>
+          <t>Geubbels</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -42191,17 +42191,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>8</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
@@ -42222,10 +42222,10 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -42303,27 +42303,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gnonto</t>
+          <t>Zeballos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F65" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
@@ -42344,13 +42344,13 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>5.75</v>
+        <v>9.5</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -42364,27 +42364,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Robinson J.</t>
+          <t>Gnonto</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
+        <v>23</v>
+      </c>
+      <c r="F66" t="n">
         <v>12</v>
-      </c>
-      <c r="F66" t="n">
-        <v>6</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -42408,10 +42408,10 @@
         <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>8.25</v>
+        <v>5.75</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -42425,7 +42425,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Robinson J.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -42442,10 +42442,10 @@
         <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -42466,10 +42466,10 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>9.5</v>
+        <v>8.25</v>
       </c>
       <c r="U67" t="n">
         <v>1</v>
@@ -42527,10 +42527,10 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>7.5</v>
+        <v>7.12</v>
       </c>
       <c r="U68" t="n">
         <v>1</v>
@@ -43077,7 +43077,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
         <v>7</v>
@@ -43124,13 +43124,13 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -43162,7 +43162,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
         <v>7</v>
@@ -43294,7 +43294,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T77" t="n">
         <v>5.5</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21090,7 +21090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA194"/>
+  <dimension ref="A1:AA195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21638,7 +21638,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -21869,27 +21869,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>De Bruyne</t>
+          <t>Zaccagni</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -21897,55 +21897,57 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>82.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>6.26</v>
+        <v>5.88</v>
       </c>
       <c r="L9" t="n">
-        <v>7.24</v>
+        <v>5.96</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.96</v>
+      </c>
       <c r="O9" t="n">
-        <v>0.447</v>
+        <v>0.772</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>7.62</v>
+        <v>6.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -21982,7 +21984,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -22156,7 +22158,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -22330,7 +22332,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -22417,7 +22419,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -22504,7 +22506,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -22591,7 +22593,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -22678,7 +22680,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -22737,27 +22739,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>McKennie</t>
+          <t>De Bruyne</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -22765,7 +22767,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -22773,46 +22775,44 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>6.13</v>
+        <v>6.26</v>
       </c>
       <c r="L19" t="n">
-        <v>6.68</v>
+        <v>7.24</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>0.86</v>
+        <v>0.447</v>
       </c>
       <c r="P19" t="n">
         <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>7.62</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ekkelenkamp</t>
+          <t>McKennie</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -22834,17 +22834,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -22860,46 +22860,46 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>6.05</v>
+        <v>6.13</v>
       </c>
       <c r="L20" t="n">
-        <v>6.61</v>
+        <v>6.68</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.842</v>
+        <v>0.86</v>
       </c>
       <c r="P20" t="n">
         <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -22911,27 +22911,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Politano</t>
+          <t>Ekkelenkamp</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>79.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -22947,28 +22947,28 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K21" t="n">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="L21" t="n">
-        <v>6.36</v>
+        <v>6.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.24</v>
+        <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -22977,16 +22977,16 @@
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>6.38</v>
+        <v>8.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -22998,27 +22998,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Modric</t>
+          <t>Politano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -23037,23 +23037,25 @@
         <v>33</v>
       </c>
       <c r="K22" t="n">
-        <v>6.45</v>
+        <v>6.09</v>
       </c>
       <c r="L22" t="n">
-        <v>6.67</v>
+        <v>6.36</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.24</v>
+      </c>
       <c r="O22" t="n">
-        <v>0.868</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -23062,10 +23064,10 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>5.88</v>
+        <v>6.38</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -23083,27 +23085,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zielinski</t>
+          <t>Modric</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -23111,7 +23113,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -23119,46 +23121,44 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K23" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.48</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>0.675</v>
+        <v>0.868</v>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>7.75</v>
+        <v>5.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -23170,27 +23170,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>Zielinski</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -23206,44 +23206,46 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="L24" t="n">
-        <v>6.59</v>
+        <v>6.8</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.48</v>
+      </c>
       <c r="O24" t="n">
-        <v>0.737</v>
+        <v>0.675</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -23255,27 +23257,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Atta</t>
+          <t>Rowe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -23283,7 +23285,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -23291,25 +23293,23 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>6.36</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>6.88</v>
+        <v>6.59</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.99</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>0.724</v>
+        <v>0.737</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
@@ -23318,10 +23318,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -23342,27 +23342,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ederson D.S.</t>
+          <t>Atta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -23370,48 +23370,48 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>70.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>6.25</v>
+        <v>6.36</v>
       </c>
       <c r="L26" t="n">
-        <v>6.43</v>
+        <v>6.88</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.09</v>
+        <v>0.99</v>
       </c>
       <c r="O26" t="n">
-        <v>0.895</v>
+        <v>0.724</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>6.75</v>
+        <v>5.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -23429,27 +23429,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Taylor K.</t>
+          <t>Ederson D.S.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -23465,44 +23465,46 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>6.06</v>
+        <v>6.25</v>
       </c>
       <c r="L27" t="n">
-        <v>6.56</v>
+        <v>6.43</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.09</v>
+      </c>
       <c r="O27" t="n">
-        <v>0.447</v>
+        <v>0.895</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -23514,27 +23516,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Konè M.</t>
+          <t>Taylor K.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -23542,36 +23544,34 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>69.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>6.26</v>
+        <v>6.06</v>
       </c>
       <c r="L28" t="n">
-        <v>6.53</v>
+        <v>6.56</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.15</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.447</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -23580,7 +23580,7 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -23589,7 +23589,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -23601,27 +23601,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zaccagni</t>
+          <t>Konè M.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -23629,57 +23629,57 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>67.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>5.88</v>
+        <v>6.26</v>
       </c>
       <c r="L29" t="n">
-        <v>5.96</v>
+        <v>6.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.96</v>
+        <v>0.15</v>
       </c>
       <c r="O29" t="n">
-        <v>0.772</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>6.5</v>
+        <v>6.12</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
@@ -23716,7 +23716,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -24025,10 +24025,10 @@
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>69.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>63.2</v>
+        <v>63.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57.6</v>
+        <v>57.9</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lobotka</t>
+          <t>Matic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -27069,17 +27069,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -27087,36 +27087,36 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>39</v>
+        <v>41.1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K71" t="n">
-        <v>6.05</v>
+        <v>5.96</v>
       </c>
       <c r="L71" t="n">
-        <v>6.1</v>
+        <v>5.96</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
-        <v>0.11</v>
+        <v>5.96</v>
       </c>
       <c r="O71" t="n">
-        <v>0.877</v>
+        <v>0.447</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -27125,19 +27125,19 @@
         <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>7.38</v>
+        <v>6.75</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
@@ -27146,21 +27146,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fazzini</t>
+          <t>Lobotka</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E72" t="n">
         <v>28</v>
@@ -27174,7 +27174,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>38.1</v>
+        <v>39.1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -27182,25 +27182,25 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K72" t="n">
-        <v>5.88</v>
+        <v>6.05</v>
       </c>
       <c r="L72" t="n">
-        <v>5.83</v>
+        <v>6.1</v>
       </c>
       <c r="M72" t="n">
         <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>-0.77</v>
+        <v>0.11</v>
       </c>
       <c r="O72" t="n">
-        <v>0.5</v>
+        <v>0.877</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -27212,16 +27212,16 @@
         <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>7.38</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -27233,27 +27233,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ndour</t>
+          <t>Fazzini</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -27269,25 +27269,25 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K73" t="n">
-        <v>5.8</v>
+        <v>5.88</v>
       </c>
       <c r="L73" t="n">
-        <v>6.07</v>
+        <v>5.83</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>0.43</v>
+        <v>-0.77</v>
       </c>
       <c r="O73" t="n">
-        <v>0.487</v>
+        <v>0.5</v>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -27299,13 +27299,13 @@
         <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>2</v>
@@ -27320,27 +27320,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Karlstrom</t>
+          <t>Ndour</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>34.2</v>
+        <v>36.1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -27356,25 +27356,25 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K74" t="n">
-        <v>5.96</v>
+        <v>5.8</v>
       </c>
       <c r="L74" t="n">
-        <v>5.96</v>
+        <v>6.07</v>
       </c>
       <c r="M74" t="n">
         <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="O74" t="n">
-        <v>0.961</v>
+        <v>0.487</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -27386,16 +27386,16 @@
         <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>6.88</v>
+        <v>5.5</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -27407,27 +27407,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Njie</t>
+          <t>Karlstrom</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F75" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>34.1</v>
+        <v>34.5</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -27443,46 +27443,46 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K75" t="n">
-        <v>5.8</v>
+        <v>5.96</v>
       </c>
       <c r="L75" t="n">
-        <v>6.15</v>
+        <v>5.96</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="O75" t="n">
-        <v>0.25</v>
+        <v>0.961</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>6.17</v>
+        <v>6.88</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -27494,27 +27494,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bakola</t>
+          <t>Njie</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F76" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>26.2</v>
+        <v>34.4</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -27530,44 +27530,46 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" t="n">
         <v>6.17</v>
       </c>
-      <c r="L76" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>3</v>
-      </c>
-      <c r="T76" t="n">
-        <v>6.5</v>
-      </c>
       <c r="U76" t="n">
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X76" t="n">
         <v>0</v>
@@ -27579,27 +27581,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cacciamani</t>
+          <t>Bakola</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>E;W</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -27607,7 +27609,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>19.4</v>
+        <v>26.3</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -27615,20 +27617,20 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="L77" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>0.026</v>
+        <v>0.079</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -27640,10 +27642,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T77" t="n">
-        <v>6.38</v>
+        <v>6.5</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -27664,27 +27666,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zhegrova</t>
+          <t>Cacciamani</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -27692,7 +27694,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -27700,20 +27702,20 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="L78" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
-        <v>0.316</v>
+        <v>0.026</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -27725,19 +27727,19 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T78" t="n">
-        <v>9.75</v>
+        <v>6.38</v>
       </c>
       <c r="U78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
@@ -27749,60 +27751,84 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Calò</t>
+          <t>Zhegrova</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>12</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L79" t="n">
+        <v>5.96</v>
+      </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T79" t="n">
-        <v>6.62</v>
+        <v>9.75</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V79" t="n">
-        <v>1</v>
-      </c>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -27810,7 +27836,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Romano</t>
+          <t>Calò</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -27820,17 +27846,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -27854,13 +27880,13 @@
         <v>4</v>
       </c>
       <c r="T80" t="n">
-        <v>7.38</v>
+        <v>6.62</v>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
@@ -27871,27 +27897,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Schmid</t>
+          <t>Romano</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -27915,13 +27941,13 @@
         <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>6</v>
+        <v>7.38</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -27932,27 +27958,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hutchinson</t>
+          <t>Schmid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -27973,16 +27999,16 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -27993,7 +28019,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Monteiro J.</t>
+          <t>Hutchinson</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -28003,17 +28029,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>7</v>
       </c>
       <c r="E83" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -28034,10 +28060,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -28054,27 +28080,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sarr P.</t>
+          <t>Monteiro J.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -28095,7 +28121,7 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
         <v>5.5</v>
@@ -28115,27 +28141,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Braganca</t>
+          <t>Sarr P.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
@@ -28156,10 +28182,10 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -28176,27 +28202,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Milla</t>
+          <t>Braganca</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -28220,7 +28246,7 @@
         <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -28237,7 +28263,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fitz-Jim</t>
+          <t>Milla</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -28247,17 +28273,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F87" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -28278,10 +28304,10 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T87" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -28298,73 +28324,51 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Thuram K.</t>
+          <t>Fitz-Jim</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="n">
+        <v>18</v>
+      </c>
+      <c r="F88" t="n">
         <v>9</v>
       </c>
-      <c r="E88" t="n">
-        <v>15</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>34</v>
-      </c>
-      <c r="K88" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>2</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="P88" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>2</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -28372,12 +28376,8 @@
       <c r="V88" t="n">
         <v>0</v>
       </c>
-      <c r="W88" t="n">
-        <v>2</v>
-      </c>
-      <c r="X88" t="n">
-        <v>0</v>
-      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
@@ -28385,27 +28385,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Odgaard</t>
+          <t>Thuram K.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>78.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -28421,37 +28421,37 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K89" t="n">
-        <v>5.91</v>
+        <v>6.1</v>
       </c>
       <c r="L89" t="n">
-        <v>6.61</v>
+        <v>6.4</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N89" t="n">
-        <v>-0.29</v>
+        <v>-0.34</v>
       </c>
       <c r="O89" t="n">
-        <v>0.518</v>
+        <v>0.882</v>
       </c>
       <c r="P89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -28460,7 +28460,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -28472,27 +28472,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Caqueret</t>
+          <t>Odgaard</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>72.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -28508,37 +28508,37 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K90" t="n">
-        <v>6.11</v>
+        <v>5.91</v>
       </c>
       <c r="L90" t="n">
-        <v>6.41</v>
+        <v>6.61</v>
       </c>
       <c r="M90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="O90" t="n">
-        <v>0.579</v>
+        <v>0.518</v>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
         <v>4</v>
       </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
       <c r="T90" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -28547,7 +28547,7 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -28559,27 +28559,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Colpani</t>
+          <t>Caqueret</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>69.3</v>
+        <v>72.3</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -28595,46 +28595,46 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K91" t="n">
-        <v>5.81</v>
+        <v>6.11</v>
       </c>
       <c r="L91" t="n">
-        <v>6.04</v>
+        <v>6.41</v>
       </c>
       <c r="M91" t="n">
         <v>2</v>
       </c>
       <c r="N91" t="n">
-        <v>-0.88</v>
+        <v>-0.37</v>
       </c>
       <c r="O91" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="P91" t="n">
         <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T91" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -28646,82 +28646,82 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Berisha M.</t>
+          <t>Colpani</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D92" t="n">
+        <v>9</v>
+      </c>
+      <c r="E92" t="n">
+        <v>15</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8</v>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>24</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="L92" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
         <v>4</v>
       </c>
-      <c r="E92" t="n">
-        <v>12</v>
-      </c>
-      <c r="F92" t="n">
-        <v>6</v>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>12</v>
-      </c>
-      <c r="K92" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="L92" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="M92" t="n">
-        <v>2</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="P92" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>3</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" t="n">
         <v>0</v>
@@ -28733,7 +28733,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Brescianini</t>
+          <t>Berisha M.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -28743,14 +28743,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>6</v>
@@ -28761,7 +28761,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -28769,37 +28769,37 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K93" t="n">
-        <v>5.97</v>
+        <v>6.17</v>
       </c>
       <c r="L93" t="n">
-        <v>6.31</v>
+        <v>6.92</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.3</v>
+        <v>0.96</v>
       </c>
       <c r="O93" t="n">
-        <v>0.667</v>
+        <v>0.342</v>
       </c>
       <c r="P93" t="n">
         <v>2</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -28808,7 +28808,7 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
         <v>0</v>
@@ -28820,24 +28820,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>El Shaarawy</t>
+          <t>Brescianini</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F94" t="n">
         <v>6</v>
@@ -28848,7 +28848,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>61.5</v>
+        <v>64.2</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -28859,34 +28859,34 @@
         <v>18</v>
       </c>
       <c r="K94" t="n">
-        <v>6.14</v>
+        <v>5.97</v>
       </c>
       <c r="L94" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="M94" t="n">
         <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="O94" t="n">
-        <v>0.596</v>
+        <v>0.667</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -28895,7 +28895,7 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Zalewski</t>
+          <t>El Shaarawy</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -28917,7 +28917,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -28935,7 +28935,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>59.2</v>
+        <v>61.7</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -28943,46 +28943,46 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K95" t="n">
-        <v>6.1</v>
+        <v>6.14</v>
       </c>
       <c r="L95" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="M95" t="n">
         <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>0.36</v>
+        <v>-0.26</v>
       </c>
       <c r="O95" t="n">
-        <v>0.632</v>
+        <v>0.596</v>
       </c>
       <c r="P95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
@@ -28994,27 +28994,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Loftus-Cheek</t>
+          <t>Addai</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
@@ -29022,54 +29022,52 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>57.8</v>
+        <v>60.5</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K96" t="n">
-        <v>6.1</v>
+        <v>5.96</v>
       </c>
       <c r="L96" t="n">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0.4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
-        <v>0.596</v>
+        <v>0.316</v>
       </c>
       <c r="P96" t="n">
         <v>3</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
       <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
         <v>4</v>
-      </c>
-      <c r="T96" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>2</v>
       </c>
       <c r="X96" t="n">
         <v>0</v>
@@ -29081,85 +29079,85 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>De Roon</t>
+          <t>Zalewski</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F97" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>31</v>
+      </c>
+      <c r="K97" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="n">
         <v>5</v>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>34</v>
-      </c>
-      <c r="K97" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="L97" t="n">
-        <v>6</v>
-      </c>
-      <c r="M97" t="n">
-        <v>3</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="P97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>2</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T97" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
@@ -29168,7 +29166,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fabbian</t>
+          <t>Loftus-Cheek</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -29178,17 +29176,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
@@ -29196,45 +29194,45 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>54.8</v>
+        <v>58</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K98" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="L98" t="n">
-        <v>6.05</v>
+        <v>6.52</v>
       </c>
       <c r="M98" t="n">
         <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.57</v>
+        <v>0.4</v>
       </c>
       <c r="O98" t="n">
-        <v>0.579</v>
+        <v>0.596</v>
       </c>
       <c r="P98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T98" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -29255,7 +29253,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Locatelli</t>
+          <t>De Roon</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -29265,17 +29263,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
@@ -29283,30 +29281,30 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>54.7</v>
+        <v>57.4</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K99" t="n">
-        <v>6.26</v>
+        <v>5.97</v>
       </c>
       <c r="L99" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="M99" t="n">
         <v>3</v>
       </c>
       <c r="N99" t="n">
-        <v>0.05</v>
+        <v>-0.32</v>
       </c>
       <c r="O99" t="n">
-        <v>0.93</v>
+        <v>0.877</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -29315,25 +29313,25 @@
         <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
@@ -29342,73 +29340,73 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Fabbian</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>12</v>
+      </c>
+      <c r="F100" t="n">
         <v>6</v>
       </c>
-      <c r="E100" t="n">
-        <v>16</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
-      </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K100" t="n">
-        <v>6.09</v>
+        <v>5.8</v>
       </c>
       <c r="L100" t="n">
-        <v>6.43</v>
+        <v>6.05</v>
       </c>
       <c r="M100" t="n">
         <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>4.42</v>
+        <v>-0.57</v>
       </c>
       <c r="O100" t="n">
-        <v>0.325</v>
+        <v>0.579</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -29417,10 +29415,10 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
@@ -29429,27 +29427,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Fadera</t>
+          <t>Locatelli</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
@@ -29457,54 +29455,54 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>51.1</v>
+        <v>54.9</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K101" t="n">
-        <v>5.92</v>
+        <v>6.26</v>
       </c>
       <c r="L101" t="n">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O101" t="n">
-        <v>0.632</v>
+        <v>0.93</v>
       </c>
       <c r="P101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
         <v>3</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -29516,7 +29514,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Nicolussi Caviglia</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -29526,11 +29524,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
         <v>16</v>
@@ -29544,7 +29542,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>50.9</v>
+        <v>54</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -29555,34 +29553,34 @@
         <v>23</v>
       </c>
       <c r="K102" t="n">
-        <v>5.89</v>
+        <v>6.09</v>
       </c>
       <c r="L102" t="n">
-        <v>6.02</v>
+        <v>6.43</v>
       </c>
       <c r="M102" t="n">
         <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.31</v>
+        <v>4.42</v>
       </c>
       <c r="O102" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.325</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -29591,10 +29589,10 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
@@ -29603,21 +29601,21 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pobega</t>
+          <t>Fadera</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
         <v>12</v>
@@ -29631,7 +29629,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>50.6</v>
+        <v>51.4</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -29639,25 +29637,25 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K103" t="n">
-        <v>5.83</v>
+        <v>5.92</v>
       </c>
       <c r="L103" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N103" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="O103" t="n">
-        <v>0.439</v>
+        <v>0.632</v>
       </c>
       <c r="P103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
@@ -29678,10 +29676,10 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
@@ -29690,73 +29688,73 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dominguez B.</t>
+          <t>Nicolussi Caviglia</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D104" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" t="n">
+        <v>16</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8</v>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>23</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="L104" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
         <v>4</v>
       </c>
-      <c r="E104" t="n">
-        <v>12</v>
-      </c>
-      <c r="F104" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>12</v>
-      </c>
-      <c r="K104" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="L104" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="M104" t="n">
-        <v>2</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>3</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -29765,7 +29763,7 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -29777,7 +29775,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ricci S.</t>
+          <t>Pobega</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -29787,11 +29785,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E105" t="n">
         <v>12</v>
@@ -29805,7 +29803,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>49.1</v>
+        <v>50.9</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -29813,38 +29811,38 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K105" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="L105" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M105" t="n">
+        <v>3</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="P105" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3</v>
+      </c>
+      <c r="T105" t="n">
         <v>6</v>
       </c>
-      <c r="L105" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="M105" t="n">
-        <v>3</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>3</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
@@ -29852,10 +29850,10 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
@@ -29864,73 +29862,73 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pessina</t>
+          <t>Dominguez B.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" t="n">
         <v>6</v>
       </c>
-      <c r="E106" t="n">
-        <v>15</v>
-      </c>
-      <c r="F106" t="n">
-        <v>8</v>
-      </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>48.1</v>
+        <v>50.1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K106" t="n">
-        <v>6.09</v>
+        <v>5.83</v>
       </c>
       <c r="L106" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="M106" t="n">
         <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.46</v>
+        <v>-0.78</v>
       </c>
       <c r="O106" t="n">
-        <v>0.632</v>
+        <v>0.421</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -29939,7 +29937,7 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -29951,73 +29949,73 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ellertsson</t>
+          <t>Ricci S.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>E;C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>12</v>
+      </c>
+      <c r="F107" t="n">
         <v>6</v>
       </c>
-      <c r="E107" t="n">
-        <v>14</v>
-      </c>
-      <c r="F107" t="n">
-        <v>7</v>
-      </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>47</v>
+        <v>49.4</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K107" t="n">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="L107" t="n">
-        <v>5.91</v>
+        <v>6.18</v>
       </c>
       <c r="M107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>-0.3</v>
+        <v>0.21</v>
       </c>
       <c r="O107" t="n">
-        <v>0.921</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -30026,10 +30024,10 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
@@ -30038,71 +30036,73 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Luis Henrique</t>
+          <t>Pessina</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>E;W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>11</v>
+      </c>
+      <c r="K108" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="L108" t="n">
         <v>6</v>
       </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>27</v>
-      </c>
-      <c r="K108" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="L108" t="n">
-        <v>6.06</v>
-      </c>
       <c r="M108" t="n">
-        <v>1</v>
-      </c>
-      <c r="N108" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-0.46</v>
+      </c>
       <c r="O108" t="n">
-        <v>0.711</v>
+        <v>0.632</v>
       </c>
       <c r="P108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -30111,7 +30111,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X108" t="n">
         <v>0</v>
@@ -30123,27 +30123,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Oristanio</t>
+          <t>Ellertsson</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>E;C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>45.1</v>
+        <v>47.2</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -30159,37 +30159,37 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K109" t="n">
-        <v>5.78</v>
+        <v>5.84</v>
       </c>
       <c r="L109" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.43</v>
+        <v>-0.3</v>
       </c>
       <c r="O109" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -30201,7 +30201,7 @@
         <v>1</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
@@ -30210,27 +30210,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Folorunsho</t>
+          <t>Luis Henrique</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>E;W</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -30246,37 +30246,35 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K110" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="L110" t="n">
-        <v>6.21</v>
+        <v>6.06</v>
       </c>
       <c r="M110" t="n">
-        <v>3</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
-        <v>0.632</v>
+        <v>0.711</v>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T110" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -30285,7 +30283,7 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X110" t="n">
         <v>0</v>
@@ -30297,27 +30295,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Busio</t>
+          <t>Oristanio</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
@@ -30325,7 +30323,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>43.4</v>
+        <v>45.3</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -30333,23 +30331,25 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K111" t="n">
-        <v>5.9</v>
+        <v>5.78</v>
       </c>
       <c r="L111" t="n">
-        <v>6.03</v>
+        <v>5.92</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
-      </c>
-      <c r="N111" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-0.43</v>
+      </c>
       <c r="O111" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="P111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -30358,19 +30358,19 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X111" t="n">
         <v>0</v>
@@ -30382,27 +30382,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Moro N.</t>
+          <t>Folorunsho</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>4</v>
       </c>
       <c r="E112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>41.4</v>
+        <v>44.3</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -30418,22 +30418,22 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K112" t="n">
-        <v>5.93</v>
+        <v>6.04</v>
       </c>
       <c r="L112" t="n">
-        <v>6.12</v>
+        <v>6.21</v>
       </c>
       <c r="M112" t="n">
         <v>3</v>
       </c>
       <c r="N112" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="O112" t="n">
-        <v>0.535</v>
+        <v>0.632</v>
       </c>
       <c r="P112" t="n">
         <v>2</v>
@@ -30445,10 +30445,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -30457,7 +30457,7 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X112" t="n">
         <v>0</v>
@@ -30469,12 +30469,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Perez K.</t>
+          <t>Busio</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -30483,13 +30483,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>41</v>
+        <v>43.7</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -30505,26 +30505,26 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K113" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L113" t="n">
         <v>6.03</v>
-      </c>
-      <c r="L113" t="n">
-        <v>6.16</v>
       </c>
       <c r="M113" t="n">
         <v>1</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
-        <v>0.421</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -30533,13 +30533,13 @@
         <v>4</v>
       </c>
       <c r="T113" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W113" t="n">
         <v>4</v>
@@ -30554,7 +30554,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Matic</t>
+          <t>Moro N.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -30564,25 +30564,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D114" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" t="n">
+        <v>14</v>
+      </c>
+      <c r="F114" t="n">
         <v>7</v>
       </c>
-      <c r="E114" t="n">
-        <v>16</v>
-      </c>
-      <c r="F114" t="n">
-        <v>8</v>
-      </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -30590,49 +30590,49 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K114" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="L114" t="n">
-        <v>5.96</v>
+        <v>6.12</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>5.96</v>
+        <v>0.02</v>
       </c>
       <c r="O114" t="n">
-        <v>0.447</v>
+        <v>0.535</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T114" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
@@ -30641,7 +30641,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dele-Bashiru</t>
+          <t>Perez K.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -30651,63 +30651,61 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D115" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" t="n">
+        <v>15</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>16</v>
+      </c>
+      <c r="K115" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L115" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
         <v>4</v>
       </c>
-      <c r="E115" t="n">
-        <v>13</v>
-      </c>
-      <c r="F115" t="n">
-        <v>6</v>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>21</v>
-      </c>
-      <c r="K115" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="L115" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="M115" t="n">
-        <v>2</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P115" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1</v>
-      </c>
       <c r="T115" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -30716,7 +30714,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X115" t="n">
         <v>0</v>
@@ -30728,21 +30726,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Adopo</t>
+          <t>Dele-Bashiru</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E116" t="n">
         <v>13</v>
@@ -30756,7 +30754,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>40.1</v>
+        <v>41</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -30764,46 +30762,46 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K116" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L116" t="n">
         <v>5.83</v>
       </c>
-      <c r="L116" t="n">
-        <v>5.88</v>
-      </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N116" t="n">
-        <v>-0.06</v>
+        <v>-0.82</v>
       </c>
       <c r="O116" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -30815,7 +30813,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Keita M.</t>
+          <t>Adopo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -30825,25 +30823,25 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D117" t="n">
+        <v>8</v>
+      </c>
+      <c r="E117" t="n">
+        <v>13</v>
+      </c>
+      <c r="F117" t="n">
         <v>6</v>
       </c>
-      <c r="E117" t="n">
-        <v>15</v>
-      </c>
-      <c r="F117" t="n">
-        <v>8</v>
-      </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -30851,22 +30849,22 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K117" t="n">
-        <v>6.01</v>
+        <v>5.83</v>
       </c>
       <c r="L117" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>0.4</v>
+        <v>-0.06</v>
       </c>
       <c r="O117" t="n">
-        <v>0.842</v>
+        <v>0.667</v>
       </c>
       <c r="P117" t="n">
         <v>1</v>
@@ -30881,16 +30879,16 @@
         <v>4</v>
       </c>
       <c r="T117" t="n">
-        <v>5.62</v>
+        <v>6.75</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -30902,7 +30900,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Piotrowski</t>
+          <t>Keita M.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -30912,17 +30910,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>6</v>
       </c>
       <c r="E118" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
@@ -30930,7 +30928,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>34.1</v>
+        <v>37.7</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -30938,44 +30936,46 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K118" t="n">
-        <v>5.88</v>
+        <v>6.01</v>
       </c>
       <c r="L118" t="n">
-        <v>5.95</v>
+        <v>6.06</v>
       </c>
       <c r="M118" t="n">
-        <v>1</v>
-      </c>
-      <c r="N118" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O118" t="n">
-        <v>0.789</v>
+        <v>0.842</v>
       </c>
       <c r="P118" t="n">
         <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T118" t="n">
-        <v>7.5</v>
+        <v>5.62</v>
       </c>
       <c r="U118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -30987,27 +30987,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sohm</t>
+          <t>Piotrowski</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>33</v>
+        <v>34.4</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -31023,46 +31023,44 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K119" t="n">
-        <v>5.65</v>
+        <v>5.88</v>
       </c>
       <c r="L119" t="n">
-        <v>5.62</v>
+        <v>5.95</v>
       </c>
       <c r="M119" t="n">
-        <v>2</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-0.64</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>0.803</v>
+        <v>0.789</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T119" t="n">
-        <v>5.17</v>
+        <v>7.5</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -31074,27 +31072,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Almqvist</t>
+          <t>Sohm</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
@@ -31102,7 +31100,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -31110,22 +31108,22 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K120" t="n">
-        <v>5.94</v>
+        <v>5.65</v>
       </c>
       <c r="L120" t="n">
-        <v>6.06</v>
+        <v>5.62</v>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N120" t="n">
-        <v>0.11</v>
+        <v>-0.64</v>
       </c>
       <c r="O120" t="n">
-        <v>0.57</v>
+        <v>0.803</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -31140,16 +31138,16 @@
         <v>3</v>
       </c>
       <c r="T120" t="n">
-        <v>6.17</v>
+        <v>5.17</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -31161,24 +31159,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gineitis</t>
+          <t>Almqvist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F121" t="n">
         <v>6</v>
@@ -31189,7 +31187,7 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -31197,19 +31195,19 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K121" t="n">
-        <v>5.87</v>
+        <v>5.94</v>
       </c>
       <c r="L121" t="n">
-        <v>5.81</v>
+        <v>6.06</v>
       </c>
       <c r="M121" t="n">
         <v>3</v>
       </c>
       <c r="N121" t="n">
-        <v>-0.3</v>
+        <v>0.11</v>
       </c>
       <c r="O121" t="n">
         <v>0.57</v>
@@ -31224,10 +31222,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T121" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -31236,7 +31234,7 @@
         <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -31248,17 +31246,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Zerbin</t>
+          <t>Gineitis</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -31276,7 +31274,7 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>31.4</v>
+        <v>32.3</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -31284,46 +31282,46 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K122" t="n">
-        <v>5.76</v>
+        <v>5.87</v>
       </c>
       <c r="L122" t="n">
-        <v>5.79</v>
+        <v>5.81</v>
       </c>
       <c r="M122" t="n">
         <v>3</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="O122" t="n">
-        <v>0.553</v>
+        <v>0.57</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -31335,21 +31333,21 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Miller L.</t>
+          <t>Zerbin</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E123" t="n">
         <v>12</v>
@@ -31363,7 +31361,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -31371,20 +31369,22 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K123" t="n">
-        <v>5.92</v>
+        <v>5.76</v>
       </c>
       <c r="L123" t="n">
-        <v>5.95</v>
+        <v>5.79</v>
       </c>
       <c r="M123" t="n">
-        <v>1</v>
-      </c>
-      <c r="N123" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="O123" t="n">
-        <v>0.5</v>
+        <v>0.553</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -31396,10 +31396,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T123" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -31408,7 +31408,7 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -31420,27 +31420,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tourè I.</t>
+          <t>Miller L.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>E;M</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>29.3</v>
+        <v>30.7</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -31456,35 +31456,35 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K124" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="L124" t="n">
-        <v>5.82</v>
+        <v>5.95</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0.789</v>
+        <v>0.5</v>
       </c>
       <c r="P124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -31496,7 +31496,7 @@
         <v>4</v>
       </c>
       <c r="X124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
@@ -31533,7 +31533,7 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -31592,27 +31592,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ilic</t>
+          <t>Tourè I.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>E;M</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E126" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F126" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -31620,33 +31620,31 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>24.7</v>
+        <v>29.4</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K126" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="L126" t="n">
-        <v>5.88</v>
+        <v>5.82</v>
       </c>
       <c r="M126" t="n">
-        <v>3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>-0.24</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
-        <v>0.456</v>
+        <v>0.789</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -31655,22 +31653,22 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
@@ -31679,62 +31677,64 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Akinsanmiro</t>
+          <t>Ilic</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F127" t="n">
+        <v>8</v>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>8</v>
+      </c>
+      <c r="K127" t="n">
         <v>6</v>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>23</v>
-      </c>
-      <c r="K127" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L127" t="n">
-        <v>5.8</v>
+        <v>5.88</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
-      </c>
-      <c r="N127" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-0.24</v>
+      </c>
       <c r="O127" t="n">
-        <v>0.605</v>
+        <v>0.456</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -31749,7 +31749,7 @@
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W127" t="n">
         <v>2</v>
@@ -31764,58 +31764,56 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Rovella</t>
+          <t>Akinsanmiro</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D128" t="n">
+        <v>7</v>
+      </c>
+      <c r="E128" t="n">
+        <v>11</v>
+      </c>
+      <c r="F128" t="n">
         <v>6</v>
       </c>
-      <c r="E128" t="n">
-        <v>16</v>
-      </c>
-      <c r="F128" t="n">
-        <v>8</v>
-      </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>21.2</v>
+        <v>23.7</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K128" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="L128" t="n">
-        <v>5.64</v>
+        <v>5.8</v>
       </c>
       <c r="M128" t="n">
-        <v>3</v>
-      </c>
-      <c r="N128" t="n">
-        <v>-0.39</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>0.57</v>
+        <v>0.605</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -31827,22 +31825,22 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T128" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" t="n">
         <v>2</v>
       </c>
       <c r="X128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
@@ -31851,7 +31849,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jashari</t>
+          <t>Rovella</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -31861,17 +31859,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E129" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
@@ -31879,7 +31877,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>19.9</v>
+        <v>21.1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -31887,20 +31885,22 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K129" t="n">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="L129" t="n">
-        <v>5.79</v>
+        <v>5.64</v>
       </c>
       <c r="M129" t="n">
-        <v>1</v>
-      </c>
-      <c r="N129" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-0.39</v>
+      </c>
       <c r="O129" t="n">
-        <v>0.316</v>
+        <v>0.57</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -31924,10 +31924,10 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
@@ -31936,21 +31936,21 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Douglas Luiz</t>
+          <t>Jashari</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
         <v>13</v>
@@ -31964,7 +31964,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>13.4</v>
+        <v>19.9</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -31972,37 +31972,35 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-5.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>0.197</v>
+        <v>0.316</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T130" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -32023,24 +32021,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ngom</t>
+          <t>Douglas Luiz</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>4</v>
       </c>
       <c r="E131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" t="n">
         <v>6</v>
@@ -32051,7 +32049,7 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>10.1</v>
+        <v>13.3</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -32059,20 +32057,22 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
-      </c>
-      <c r="N131" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-5.8</v>
+      </c>
       <c r="O131" t="n">
-        <v>0.342</v>
+        <v>0.197</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -32087,7 +32087,7 @@
         <v>4</v>
       </c>
       <c r="T131" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -32096,7 +32096,7 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Amorim</t>
+          <t>Ngom</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -32118,14 +32118,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F132" t="n">
         <v>6</v>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -32144,20 +32144,20 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K132" t="n">
-        <v>5.72</v>
+        <v>5.69</v>
       </c>
       <c r="L132" t="n">
-        <v>5.67</v>
+        <v>5.65</v>
       </c>
       <c r="M132" t="n">
         <v>1</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="n">
-        <v>0.237</v>
+        <v>0.342</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -32193,21 +32193,21 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fini</t>
+          <t>Amorim</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E133" t="n">
         <v>11</v>
@@ -32221,7 +32221,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -32229,20 +32229,20 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K133" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="L133" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M133" t="n">
         <v>1</v>
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
-        <v>0.026</v>
+        <v>0.237</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -32254,10 +32254,10 @@
         <v>0</v>
       </c>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T133" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -32266,7 +32266,7 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" t="n">
         <v>0</v>
@@ -32278,24 +32278,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Gorter</t>
+          <t>Fini</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F134" t="n">
         <v>6</v>
@@ -32306,7 +32306,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -32339,13 +32339,13 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T134" t="n">
-        <v>7.5</v>
+        <v>6.12</v>
       </c>
       <c r="U134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -32363,24 +32363,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Liberali</t>
+          <t>Gorter</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F135" t="n">
         <v>6</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -32399,22 +32399,20 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -32426,13 +32424,13 @@
         <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T135" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -32450,51 +32448,73 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Winks</t>
+          <t>Liberali</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F136" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
       <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -32502,8 +32522,12 @@
       <c r="V136" t="n">
         <v>0</v>
       </c>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr"/>
@@ -32511,27 +32535,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Unai Gomez</t>
+          <t>Winks</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>7</v>
       </c>
       <c r="E137" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
@@ -32552,16 +32576,16 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
@@ -32572,27 +32596,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Unai Gomez</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>7</v>
       </c>
       <c r="E138" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
@@ -32613,10 +32637,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T138" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -32633,7 +32657,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Oulai</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -32643,14 +32667,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E139" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
         <v>8</v>
@@ -32674,16 +32698,16 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T139" t="n">
-        <v>5.67</v>
+        <v>5.88</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
@@ -32694,7 +32718,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Amondarain</t>
+          <t>Oulai</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -32704,17 +32728,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E140" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F140" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
@@ -32735,10 +32759,10 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T140" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -32755,7 +32779,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cichella</t>
+          <t>Amondarain</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -32765,14 +32789,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>4</v>
       </c>
       <c r="E141" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F141" t="n">
         <v>6</v>
@@ -32799,7 +32823,7 @@
         <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -32816,24 +32840,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Meichtry</t>
+          <t>Cichella</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>W;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F142" t="n">
         <v>6</v>
@@ -32860,7 +32884,7 @@
         <v>2</v>
       </c>
       <c r="T142" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -32877,24 +32901,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Massolin</t>
+          <t>Meichtry</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W;T</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D143" t="n">
         <v>4</v>
       </c>
       <c r="E143" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F143" t="n">
         <v>6</v>
@@ -32918,10 +32942,10 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -32938,21 +32962,21 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Diallo O.</t>
+          <t>Massolin</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
         <v>12</v>
@@ -32979,10 +33003,10 @@
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -32999,21 +33023,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mout</t>
+          <t>Diallo O.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
         <v>12</v>
@@ -33043,7 +33067,7 @@
         <v>1</v>
       </c>
       <c r="T145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -33060,7 +33084,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Mkhitaryan</t>
+          <t>Mout</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -33070,63 +33094,41 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F146" t="n">
-        <v>4</v>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
-        <v>28</v>
-      </c>
-      <c r="K146" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="L146" t="n">
-        <v>6.59</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>3</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="P146" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>1</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
       <c r="S146" t="n">
         <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -33134,12 +33136,8 @@
       <c r="V146" t="n">
         <v>0</v>
       </c>
-      <c r="W146" t="n">
-        <v>5</v>
-      </c>
-      <c r="X146" t="n">
-        <v>0</v>
-      </c>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr"/>
@@ -33147,82 +33145,82 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>El Azzouzi O.</t>
+          <t>Mkhitaryan</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F147" t="n">
+        <v>4</v>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>28</v>
+      </c>
+      <c r="K147" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="L147" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="M147" t="n">
+        <v>3</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="P147" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
         <v>5</v>
-      </c>
-      <c r="G147" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>71</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="n">
-        <v>3</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-2.56</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="n">
-        <v>1</v>
-      </c>
-      <c r="T147" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U147" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" t="n">
-        <v>0</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -33234,7 +33232,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cataldi</t>
+          <t>El Azzouzi O.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -33244,11 +33242,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
         <v>10</v>
@@ -33262,7 +33260,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -33270,37 +33268,37 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>3</v>
       </c>
       <c r="N148" t="n">
-        <v>0.18</v>
+        <v>-2.56</v>
       </c>
       <c r="O148" t="n">
-        <v>0.64</v>
+        <v>0.079</v>
       </c>
       <c r="P148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -33309,7 +33307,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -33321,21 +33319,21 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Addai</t>
+          <t>Cataldi</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
         <v>10</v>
@@ -33349,7 +33347,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>60.4</v>
+        <v>62.8</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -33357,29 +33355,31 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K149" t="n">
-        <v>5.96</v>
+        <v>6.07</v>
       </c>
       <c r="L149" t="n">
-        <v>6.54</v>
+        <v>6.41</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
-      </c>
-      <c r="N149" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.18</v>
+      </c>
       <c r="O149" t="n">
-        <v>0.316</v>
+        <v>0.64</v>
       </c>
       <c r="P149" t="n">
         <v>3</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -33394,7 +33394,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sulemana I.</t>
+          <t>Ilkhan</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -33762,14 +33762,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F154" t="n">
         <v>4</v>
@@ -33780,7 +33780,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -33788,37 +33788,37 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>5.69</v>
+        <v>5.82</v>
       </c>
       <c r="L154" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="M154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N154" t="n">
-        <v>-0.9399999999999999</v>
+        <v>6</v>
       </c>
       <c r="O154" t="n">
-        <v>0.377</v>
+        <v>0.224</v>
       </c>
       <c r="P154" t="n">
         <v>1</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T154" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -33827,10 +33827,10 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
@@ -33839,7 +33839,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ilkhan</t>
+          <t>Sulemana I.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -33849,14 +33849,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F155" t="n">
         <v>4</v>
@@ -33867,7 +33867,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -33875,38 +33875,38 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K155" t="n">
-        <v>5.82</v>
+        <v>5.69</v>
       </c>
       <c r="L155" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
         <v>6</v>
       </c>
-      <c r="M155" t="n">
-        <v>2</v>
-      </c>
-      <c r="N155" t="n">
-        <v>6</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="P155" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>2</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>2</v>
-      </c>
-      <c r="T155" t="n">
-        <v>5.5</v>
-      </c>
       <c r="U155" t="n">
         <v>0</v>
       </c>
@@ -33914,10 +33914,10 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
@@ -33926,27 +33926,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Gilmour</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>37.8</v>
+        <v>38.1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -33962,25 +33962,25 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K156" t="n">
-        <v>6.08</v>
+        <v>5.86</v>
       </c>
       <c r="L156" t="n">
-        <v>6.27</v>
+        <v>5.79</v>
       </c>
       <c r="M156" t="n">
         <v>2</v>
       </c>
       <c r="N156" t="n">
-        <v>0.21</v>
+        <v>-0.67</v>
       </c>
       <c r="O156" t="n">
-        <v>0.395</v>
+        <v>0.526</v>
       </c>
       <c r="P156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
@@ -33989,10 +33989,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -34001,7 +34001,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -34013,27 +34013,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Gilmour</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -34049,25 +34049,25 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K157" t="n">
-        <v>5.86</v>
+        <v>6.08</v>
       </c>
       <c r="L157" t="n">
-        <v>5.79</v>
+        <v>6.27</v>
       </c>
       <c r="M157" t="n">
         <v>2</v>
       </c>
       <c r="N157" t="n">
-        <v>-0.67</v>
+        <v>0.21</v>
       </c>
       <c r="O157" t="n">
-        <v>0.526</v>
+        <v>0.395</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -34076,10 +34076,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -34088,7 +34088,7 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
@@ -34128,7 +34128,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -34735,11 +34735,11 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -34822,7 +34822,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -35138,27 +35138,27 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Venturino</t>
+          <t>Gelli F.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -35174,22 +35174,20 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K170" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="L170" t="n">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="M170" t="n">
-        <v>2</v>
-      </c>
-      <c r="N170" t="n">
-        <v>-2.97</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="n">
-        <v>0.132</v>
+        <v>0.526</v>
       </c>
       <c r="P170" t="n">
         <v>0</v>
@@ -35213,7 +35211,7 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X170" t="n">
         <v>0</v>
@@ -35225,27 +35223,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Gelli F.</t>
+          <t>Venturino</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
@@ -35261,20 +35259,22 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K171" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="L171" t="n">
-        <v>5.78</v>
+        <v>5.86</v>
       </c>
       <c r="M171" t="n">
-        <v>1</v>
-      </c>
-      <c r="N171" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-2.97</v>
+      </c>
       <c r="O171" t="n">
-        <v>0.526</v>
+        <v>0.132</v>
       </c>
       <c r="P171" t="n">
         <v>0</v>
@@ -35298,7 +35298,7 @@
         <v>0</v>
       </c>
       <c r="W171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X171" t="n">
         <v>0</v>
@@ -35338,7 +35338,7 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Liteta</t>
+          <t>Sierro</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -36259,11 +36259,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
@@ -36271,49 +36271,29 @@
       <c r="F185" t="n">
         <v>1</v>
       </c>
-      <c r="G185" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H185" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J185" t="n">
-        <v>4</v>
-      </c>
-      <c r="K185" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L185" t="n">
-        <v>5.75</v>
-      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
       <c r="M185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
-      </c>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
       <c r="S185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -36321,12 +36301,8 @@
       <c r="V185" t="n">
         <v>0</v>
       </c>
-      <c r="W185" t="n">
-        <v>0</v>
-      </c>
-      <c r="X185" t="n">
-        <v>0</v>
-      </c>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="inlineStr"/>
       <c r="AA185" t="inlineStr"/>
@@ -36334,17 +36310,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Fofana Sa.</t>
+          <t>Lovric</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -36362,34 +36338,36 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>8.4</v>
+        <v>29.7</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K186" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="L186" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="M186" t="n">
-        <v>1</v>
-      </c>
-      <c r="N186" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N186" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="O186" t="n">
-        <v>0.053</v>
+        <v>0.649</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -36407,7 +36385,7 @@
         <v>0</v>
       </c>
       <c r="W186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X186" t="n">
         <v>0</v>
@@ -36419,17 +36397,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lahdo</t>
+          <t>Liteta</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -36447,7 +36425,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>6.4</v>
+        <v>10.6</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -36455,20 +36433,20 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K187" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M187" t="n">
         <v>1</v>
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
@@ -36504,7 +36482,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Sierro</t>
+          <t>Fofana Sa.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -36514,11 +36492,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -36531,24 +36509,44 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="H188" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L188" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
+      <c r="O188" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -36556,8 +36554,12 @@
       <c r="V188" t="n">
         <v>0</v>
       </c>
-      <c r="W188" t="inlineStr"/>
-      <c r="X188" t="inlineStr"/>
+      <c r="W188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" t="n">
+        <v>0</v>
+      </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="inlineStr"/>
       <c r="AA188" t="inlineStr"/>
@@ -36565,17 +36567,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>El Azzouzi A.</t>
+          <t>Lahdo</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>C;T</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -36592,19 +36594,39 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
       <c r="S189" t="n">
         <v>0</v>
       </c>
@@ -36617,8 +36639,12 @@
       <c r="V189" t="n">
         <v>0</v>
       </c>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr"/>
+      <c r="W189" t="n">
+        <v>0</v>
+      </c>
+      <c r="X189" t="n">
+        <v>0</v>
+      </c>
       <c r="Y189" t="inlineStr"/>
       <c r="Z189" t="inlineStr"/>
       <c r="AA189" t="inlineStr"/>
@@ -36626,17 +36652,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Dagasso</t>
+          <t>El Azzouzi A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -36667,10 +36693,10 @@
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T190" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U190" t="n">
         <v>0</v>
@@ -36687,17 +36713,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Laerke</t>
+          <t>Dagasso</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>W;A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -36728,10 +36754,10 @@
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T191" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U191" t="n">
         <v>0</v>
@@ -36748,17 +36774,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Comotto</t>
+          <t>Laerke</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>M;C</t>
+          <t>W;A</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -36809,17 +36835,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ciervo</t>
+          <t>Comotto</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M;C</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -36870,17 +36896,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Libra</t>
+          <t>Ciervo</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>C;T</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -36911,10 +36937,10 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T194" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U194" t="n">
         <v>0</v>
@@ -36928,8 +36954,69 @@
       <c r="Z194" t="inlineStr"/>
       <c r="AA194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Libra</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>C;T</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="n">
+        <v>1</v>
+      </c>
+      <c r="T195" t="n">
+        <v>5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA194"/>
+  <autoFilter ref="A1:AA195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
@@ -5637,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA191"/>
+  <dimension ref="A1:AA192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8448,21 +8448,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chalobah T.</t>
+          <t>Alaba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
         <v>25</v>
@@ -8489,10 +8489,10 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -8509,12 +8509,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Couto</t>
+          <t>Chalobah T.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8523,13 +8523,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -8550,16 +8550,16 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -8570,27 +8570,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Theate</t>
+          <t>Couto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -8611,16 +8611,16 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -11138,21 +11138,21 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Provstgaard</t>
+          <t>Doig</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
         <v>12</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>36.7</v>
+        <v>35.8</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -11174,22 +11174,22 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K65" t="n">
-        <v>5.91</v>
+        <v>5.85</v>
       </c>
       <c r="L65" t="n">
-        <v>5.85</v>
+        <v>5.76</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>-0.65</v>
+        <v>-0.01</v>
       </c>
       <c r="O65" t="n">
-        <v>0.316</v>
+        <v>0.724</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -11204,16 +11204,16 @@
         <v>5</v>
       </c>
       <c r="T65" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -11225,7 +11225,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Doig</t>
+          <t>Estupinan</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11235,14 +11235,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" t="n">
         <v>6</v>
@@ -11253,7 +11253,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -11261,40 +11261,38 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="L66" t="n">
-        <v>5.76</v>
+        <v>5.71</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-0.01</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>0.724</v>
+        <v>0.368</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="n">
-        <v>6.7</v>
+        <v>5.75</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -11303,7 +11301,7 @@
         <v>5</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
@@ -11312,27 +11310,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Estupinan</t>
+          <t>Heggem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
@@ -11340,7 +11338,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>35.7</v>
+        <v>33.8</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -11348,35 +11346,35 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>5.64</v>
+        <v>5.84</v>
       </c>
       <c r="L67" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="M67" t="n">
         <v>1</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>0.368</v>
+        <v>0.658</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T67" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11385,7 +11383,7 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
         <v>1</v>
@@ -11397,7 +11395,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Heggem</t>
+          <t>Rodriguez Ju.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11407,11 +11405,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
         <v>14</v>
@@ -11425,7 +11423,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -11433,23 +11431,23 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K68" t="n">
-        <v>5.84</v>
+        <v>5.62</v>
       </c>
       <c r="L68" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>0.658</v>
+        <v>0.421</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11461,7 +11459,7 @@
         <v>5</v>
       </c>
       <c r="T68" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -11470,10 +11468,10 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
@@ -11482,21 +11480,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Rodriguez Ju.</t>
+          <t>Troilo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
         <v>14</v>
@@ -11510,7 +11508,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>33.6</v>
+        <v>30.1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -11518,20 +11516,20 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>5.62</v>
+        <v>5.79</v>
       </c>
       <c r="L69" t="n">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
       <c r="M69" t="n">
         <v>1</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>0.421</v>
+        <v>0.553</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -11546,7 +11544,7 @@
         <v>5</v>
       </c>
       <c r="T69" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -11555,10 +11553,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
@@ -11567,27 +11565,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Troilo</t>
+          <t>Veiga D.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
@@ -11595,7 +11593,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -11603,23 +11601,25 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K70" t="n">
-        <v>5.79</v>
+        <v>5.82</v>
       </c>
       <c r="L70" t="n">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="O70" t="n">
-        <v>0.553</v>
+        <v>0.618</v>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11631,19 +11631,19 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
@@ -11652,27 +11652,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Veiga D.</t>
+          <t>Zè Pedro</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>29.6</v>
+        <v>26.9</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -11688,28 +11688,26 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K71" t="n">
-        <v>5.82</v>
+        <v>5.77</v>
       </c>
       <c r="L71" t="n">
-        <v>5.69</v>
+        <v>5.68</v>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-0.04</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>0.618</v>
+        <v>0.579</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -11718,16 +11716,16 @@
         <v>5</v>
       </c>
       <c r="T71" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -11739,27 +11737,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zè Pedro</t>
+          <t>Marin R.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
@@ -11767,7 +11765,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -11775,26 +11773,26 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="L72" t="n">
-        <v>5.68</v>
+        <v>5.83</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>0.579</v>
+        <v>0.079</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -11803,7 +11801,7 @@
         <v>5</v>
       </c>
       <c r="T72" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -11812,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -11824,24 +11822,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marin R.</t>
+          <t>Helland</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
         <v>6</v>
@@ -11852,7 +11850,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>23.9</v>
+        <v>9.9</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -11860,20 +11858,20 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L73" t="n">
-        <v>5.83</v>
+        <v>5.33</v>
       </c>
       <c r="M73" t="n">
         <v>1</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>0.079</v>
+        <v>0.158</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -11885,10 +11883,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>5.4</v>
+        <v>6.17</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -11897,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -11909,7 +11907,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Helland</t>
+          <t>Abankwah</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -11919,70 +11917,72 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D74" t="n">
+        <v>7</v>
+      </c>
+      <c r="E74" t="n">
+        <v>14</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>6</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
         <v>5</v>
       </c>
-      <c r="E74" t="n">
-        <v>12</v>
-      </c>
-      <c r="F74" t="n">
-        <v>6</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>6</v>
-      </c>
-      <c r="K74" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L74" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3</v>
-      </c>
       <c r="T74" t="n">
-        <v>6.17</v>
+        <v>6.7</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -11994,21 +11994,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Abankwah</t>
+          <t>Stones</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E75" t="n">
         <v>14</v>
@@ -12021,59 +12021,33 @@
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H75" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>2</v>
-      </c>
-      <c r="K75" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L75" t="n">
-        <v>6</v>
-      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>6</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T75" t="n">
-        <v>6.7</v>
+        <v>5.83</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
       </c>
-      <c r="W75" t="n">
-        <v>1</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
@@ -12081,27 +12055,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Stones</t>
+          <t>Kaiki</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
@@ -12122,13 +12096,13 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>5.83</v>
+        <v>7.75</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -12142,17 +12116,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kaiki</t>
+          <t>Bracaglia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -12183,16 +12157,16 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T77" t="n">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -12203,12 +12177,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bracaglia</t>
+          <t>Calvani</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12217,13 +12191,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -12247,13 +12221,13 @@
         <v>5</v>
       </c>
       <c r="T78" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -12264,7 +12238,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Calvani</t>
+          <t>Doekhi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12274,7 +12248,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -12305,16 +12279,16 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>6.3</v>
+        <v>6.67</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
@@ -12325,24 +12299,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Doekhi</t>
+          <t>Leysen F.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F80" t="n">
         <v>6</v>
@@ -12366,10 +12340,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -12386,7 +12360,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leysen F.</t>
+          <t>Theate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12396,17 +12370,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -12427,16 +12401,16 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>6.3</v>
+        <v>5.83</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -15091,21 +15065,21 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Britschgi</t>
+          <t>Provstgaard</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
         <v>12</v>
@@ -15119,7 +15093,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -15127,35 +15101,37 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K114" t="n">
-        <v>5.75</v>
+        <v>5.91</v>
       </c>
       <c r="L114" t="n">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
-      </c>
-      <c r="N114" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="O114" t="n">
-        <v>0.737</v>
+        <v>0.316</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T114" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -15164,10 +15140,10 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
@@ -15176,85 +15152,83 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Walukiewicz</t>
+          <t>Britschgi</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>28</v>
+      </c>
+      <c r="K115" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>2</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>3</v>
+      </c>
+      <c r="T115" t="n">
+        <v>6</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
         <v>5</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>34</v>
-      </c>
-      <c r="K115" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="L115" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="M115" t="n">
-        <v>3</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>7</v>
-      </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
@@ -15263,27 +15237,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Floriani Mussolini</t>
+          <t>Walukiewicz</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
@@ -15291,7 +15265,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>34.2</v>
+        <v>35.5</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -15299,20 +15273,22 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K116" t="n">
-        <v>5.72</v>
+        <v>5.81</v>
       </c>
       <c r="L116" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O116" t="n">
-        <v>0.605</v>
+        <v>0.781</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -15324,10 +15300,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -15336,7 +15312,7 @@
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -15348,7 +15324,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Smolcic I.</t>
+          <t>Floriani Mussolini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15358,63 +15334,61 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>23</v>
+      </c>
+      <c r="K117" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
         <v>5</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>25</v>
-      </c>
-      <c r="K117" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="L117" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="M117" t="n">
-        <v>2</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1</v>
-      </c>
       <c r="T117" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -15423,7 +15397,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -15435,21 +15409,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mazzocchi</t>
+          <t>Smolcic I.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
         <v>10</v>
@@ -15463,7 +15437,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -15471,22 +15445,22 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K118" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="L118" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N118" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="O118" t="n">
-        <v>0.386</v>
+        <v>0.434</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -15498,10 +15472,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -15510,10 +15484,10 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
@@ -15522,62 +15496,64 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Vitik</t>
+          <t>Mazzocchi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
         <v>9</v>
-      </c>
-      <c r="F119" t="n">
-        <v>4</v>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>18</v>
       </c>
       <c r="K119" t="n">
         <v>5.94</v>
       </c>
       <c r="L119" t="n">
-        <v>5.86</v>
+        <v>5.94</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
-      </c>
-      <c r="N119" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.29</v>
+      </c>
       <c r="O119" t="n">
-        <v>0.474</v>
+        <v>0.386</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -15595,10 +15571,10 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
@@ -15607,7 +15583,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ghilardi</t>
+          <t>Vitik</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15617,11 +15593,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E120" t="n">
         <v>9</v>
@@ -15635,7 +15611,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -15643,22 +15619,20 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K120" t="n">
-        <v>5.98</v>
+        <v>5.94</v>
       </c>
       <c r="L120" t="n">
-        <v>5.95</v>
+        <v>5.86</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0.41</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
-        <v>0.592</v>
+        <v>0.474</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -15670,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -15682,7 +15656,7 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15694,7 +15668,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gaspar K.</t>
+          <t>Ghilardi</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15704,45 +15678,45 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>9</v>
+      </c>
+      <c r="F121" t="n">
         <v>4</v>
       </c>
-      <c r="E121" t="n">
-        <v>12</v>
-      </c>
-      <c r="F121" t="n">
-        <v>6</v>
-      </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>31</v>
+        <v>32.4</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J121" t="n">
         <v>21</v>
       </c>
       <c r="K121" t="n">
-        <v>5.83</v>
+        <v>5.98</v>
       </c>
       <c r="L121" t="n">
-        <v>5.64</v>
+        <v>5.95</v>
       </c>
       <c r="M121" t="n">
         <v>2</v>
       </c>
       <c r="N121" t="n">
-        <v>-0.51</v>
+        <v>0.41</v>
       </c>
       <c r="O121" t="n">
         <v>0.592</v>
@@ -15757,10 +15731,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -15769,10 +15743,10 @@
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
@@ -15781,7 +15755,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pongracic</t>
+          <t>Gaspar K.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15791,60 +15765,60 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E122" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F122" t="n">
+        <v>6</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>31</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>21</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="L122" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
         <v>4</v>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>35</v>
-      </c>
-      <c r="K122" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="L122" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M122" t="n">
-        <v>3</v>
-      </c>
-      <c r="N122" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1</v>
       </c>
       <c r="T122" t="n">
         <v>5</v>
@@ -15856,10 +15830,10 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
@@ -15868,80 +15842,82 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Oyono A.</t>
+          <t>Pongracic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F123" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>35</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="L123" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" t="n">
         <v>5</v>
       </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>14</v>
-      </c>
-      <c r="K123" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="L123" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M123" t="n">
-        <v>1</v>
-      </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>1</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>5</v>
-      </c>
-      <c r="T123" t="n">
-        <v>6.5</v>
-      </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -15953,27 +15929,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Arizala</t>
+          <t>Oyono A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E124" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
@@ -15981,7 +15957,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>25.6</v>
+        <v>28.1</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -15989,44 +15965,44 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K124" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="L124" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0.132</v>
+        <v>0.368</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X124" t="n">
         <v>0</v>
@@ -16038,56 +16014,56 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bella-Kotchap</t>
+          <t>Arizala</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" t="n">
         <v>4</v>
       </c>
-      <c r="E125" t="n">
-        <v>11</v>
-      </c>
-      <c r="F125" t="n">
-        <v>6</v>
-      </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K125" t="n">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="L125" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="M125" t="n">
         <v>1</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
-        <v>0.474</v>
+        <v>0.132</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -16099,10 +16075,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -16111,7 +16087,7 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
@@ -16123,12 +16099,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Juan Jesus</t>
+          <t>Bella-Kotchap</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -16140,57 +16116,55 @@
         <v>4</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F126" t="n">
+        <v>6</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>18</v>
+      </c>
+      <c r="K126" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="L126" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>2</v>
+      </c>
+      <c r="T126" t="n">
         <v>5</v>
       </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>21</v>
-      </c>
-      <c r="K126" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="L126" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>2</v>
-      </c>
-      <c r="T126" t="n">
-        <v>5.5</v>
-      </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
@@ -16198,10 +16172,10 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="X126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
@@ -16210,27 +16184,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cittadini</t>
+          <t>Juan Jesus</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>4</v>
       </c>
       <c r="E127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
@@ -16238,28 +16212,30 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>23.9</v>
+        <v>24.7</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K127" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="L127" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
-      </c>
-      <c r="N127" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="O127" t="n">
-        <v>0.079</v>
+        <v>0.509</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -16271,10 +16247,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T127" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -16283,10 +16259,10 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
@@ -16295,7 +16271,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Schingtienne</t>
+          <t>Cittadini</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16305,17 +16281,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
@@ -16323,7 +16299,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>17</v>
+        <v>23.9</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -16331,20 +16307,20 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L128" t="n">
-        <v>5.63</v>
+        <v>5.83</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>0.395</v>
+        <v>0.079</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -16359,7 +16335,7 @@
         <v>5</v>
       </c>
       <c r="T128" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16368,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X128" t="n">
         <v>0</v>
@@ -16380,7 +16356,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Schingtienne</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -16390,17 +16366,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
@@ -16408,28 +16384,28 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K129" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L129" t="n">
-        <v>5.5</v>
+        <v>5.63</v>
       </c>
       <c r="M129" t="n">
         <v>1</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>0.105</v>
+        <v>0.395</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -16441,10 +16417,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T129" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -16453,7 +16429,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -16465,7 +16441,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ndiaye</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16475,11 +16451,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
         <v>8</v>
@@ -16493,7 +16469,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>11.7</v>
+        <v>14.9</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -16501,20 +16477,20 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K130" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="L130" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="M130" t="n">
         <v>1</v>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>0.289</v>
+        <v>0.105</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -16529,7 +16505,7 @@
         <v>1</v>
       </c>
       <c r="T130" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -16538,10 +16514,10 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
@@ -16550,7 +16526,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lucchesi</t>
+          <t>Ndiaye</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -16560,46 +16536,46 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>8</v>
+      </c>
+      <c r="F131" t="n">
         <v>4</v>
       </c>
-      <c r="E131" t="n">
-        <v>12</v>
-      </c>
-      <c r="F131" t="n">
-        <v>6</v>
-      </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H131" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
         <v>11</v>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="M131" t="n">
         <v>1</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -16611,10 +16587,10 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -16623,10 +16599,10 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
@@ -16635,7 +16611,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Koulierakis</t>
+          <t>Lucchesi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -16645,41 +16621,61 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>11</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T132" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -16687,8 +16683,12 @@
       <c r="V132" t="n">
         <v>0</v>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
@@ -16696,24 +16696,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Correia T.</t>
+          <t>Koulierakis</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -16737,7 +16737,7 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T133" t="n">
         <v>6</v>
@@ -16757,17 +16757,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Badiashile</t>
+          <t>Correia T.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -16798,10 +16798,10 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -16818,7 +16818,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Caleta-Car</t>
+          <t>Badiashile</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -16828,17 +16828,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D135" t="n">
         <v>6</v>
       </c>
       <c r="E135" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -16879,27 +16879,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sugawara</t>
+          <t>Caleta-Car</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F136" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
         <v>6</v>
@@ -16940,27 +16940,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Leite</t>
+          <t>Sugawara</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>6</v>
       </c>
       <c r="E137" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F137" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
@@ -16981,10 +16981,10 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -17001,27 +17001,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Valdepenas</t>
+          <t>Leite</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
@@ -17042,10 +17042,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -17062,27 +17062,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Valdepenas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>5</v>
       </c>
       <c r="E139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -17103,10 +17103,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T139" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -17123,17 +17123,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cinquegrano</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -17164,16 +17164,16 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T140" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
@@ -17184,7 +17184,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Cinquegrano</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -17194,17 +17194,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>5</v>
       </c>
       <c r="E141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -17225,16 +17225,16 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T141" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -17245,21 +17245,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lulli</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E142" t="n">
         <v>10</v>
@@ -17286,10 +17286,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T142" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -17306,27 +17306,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Drameh</t>
+          <t>Lulli</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
@@ -17347,10 +17347,10 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -17367,68 +17367,46 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Beukema</t>
+          <t>Drameh</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F144" t="n">
         <v>4</v>
       </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>22</v>
-      </c>
-      <c r="K144" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="L144" t="n">
-        <v>6.16</v>
-      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>3</v>
-      </c>
-      <c r="N144" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="P144" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
         <v>0</v>
       </c>
@@ -17441,12 +17419,8 @@
       <c r="V144" t="n">
         <v>0</v>
       </c>
-      <c r="W144" t="n">
-        <v>2</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
@@ -17454,35 +17428,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cabal</t>
+          <t>Beukema</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" t="n">
+        <v>7</v>
+      </c>
+      <c r="F145" t="n">
         <v>4</v>
       </c>
-      <c r="F145" t="n">
-        <v>2</v>
-      </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>65.2</v>
+        <v>67.3</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -17490,22 +17464,22 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K145" t="n">
-        <v>5.94</v>
+        <v>5.93</v>
       </c>
       <c r="L145" t="n">
-        <v>6.56</v>
+        <v>6.16</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="O145" t="n">
-        <v>0.298</v>
+        <v>0.754</v>
       </c>
       <c r="P145" t="n">
         <v>2</v>
@@ -17529,7 +17503,7 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17541,24 +17515,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Idrissi R.</t>
+          <t>Cabal</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
@@ -17569,7 +17543,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>62.3</v>
+        <v>65.2</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -17577,20 +17551,22 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K146" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="L146" t="n">
-        <v>6.09</v>
+        <v>6.56</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
-      </c>
-      <c r="N146" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.53</v>
+      </c>
       <c r="O146" t="n">
-        <v>0.447</v>
+        <v>0.298</v>
       </c>
       <c r="P146" t="n">
         <v>2</v>
@@ -17614,7 +17590,7 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17626,24 +17602,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>De Silvestri</t>
+          <t>Idrissi R.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
         <v>2</v>
@@ -17654,7 +17630,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>50.2</v>
+        <v>62.3</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -17662,25 +17638,23 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="L147" t="n">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="M147" t="n">
-        <v>3</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-0.34</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
-        <v>0.333</v>
+        <v>0.447</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -17689,10 +17663,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -17701,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -17713,27 +17687,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pellegrini Lu.</t>
+          <t>De Silvestri</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
@@ -17741,7 +17715,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.8</v>
+        <v>50.2</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -17749,25 +17723,25 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K148" t="n">
-        <v>5.85</v>
+        <v>6.05</v>
       </c>
       <c r="L148" t="n">
-        <v>5.81</v>
+        <v>5.95</v>
       </c>
       <c r="M148" t="n">
         <v>3</v>
       </c>
       <c r="N148" t="n">
-        <v>-0.17</v>
+        <v>-0.34</v>
       </c>
       <c r="O148" t="n">
-        <v>0.526</v>
+        <v>0.333</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -17776,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -17788,7 +17762,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -17800,27 +17774,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Van Der Brempt</t>
+          <t>Pellegrini Lu.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
@@ -17828,7 +17802,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>43.4</v>
+        <v>47.8</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -17836,28 +17810,28 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K149" t="n">
-        <v>5.96</v>
+        <v>5.85</v>
       </c>
       <c r="L149" t="n">
-        <v>5.96</v>
+        <v>5.81</v>
       </c>
       <c r="M149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="O149" t="n">
-        <v>0.421</v>
+        <v>0.526</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -17875,7 +17849,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -17887,27 +17861,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sverko</t>
+          <t>Van Der Brempt</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
@@ -17915,7 +17889,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -17926,23 +17900,25 @@
         <v>14</v>
       </c>
       <c r="K150" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="L150" t="n">
-        <v>5.86</v>
+        <v>5.96</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
-      </c>
-      <c r="N150" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.04</v>
+      </c>
       <c r="O150" t="n">
-        <v>0.368</v>
+        <v>0.421</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -17960,7 +17936,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -17972,35 +17948,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Terracciano F.</t>
+          <t>Sverko</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B;Dd;Ds</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F151" t="n">
         <v>4</v>
       </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -18008,25 +17984,23 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K151" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L151" t="n">
         <v>5.86</v>
       </c>
-      <c r="L151" t="n">
-        <v>5.83</v>
-      </c>
       <c r="M151" t="n">
-        <v>3</v>
-      </c>
-      <c r="N151" t="n">
-        <v>0.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="n">
-        <v>0.535</v>
+        <v>0.368</v>
       </c>
       <c r="P151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -18047,7 +18021,7 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X151" t="n">
         <v>0</v>
@@ -18059,24 +18033,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Biraghi</t>
+          <t>Terracciano F.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>B;Dd;Ds</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F152" t="n">
         <v>2</v>
@@ -18087,7 +18061,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -18095,25 +18069,25 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K152" t="n">
-        <v>5.59</v>
+        <v>5.86</v>
       </c>
       <c r="L152" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="M152" t="n">
         <v>3</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="O152" t="n">
-        <v>0.526</v>
+        <v>0.535</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
@@ -18134,7 +18108,7 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X152" t="n">
         <v>0</v>
@@ -18146,17 +18120,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Lazzari</t>
+          <t>Biraghi</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -18174,7 +18148,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>32</v>
+        <v>35.2</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -18182,22 +18156,22 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K153" t="n">
-        <v>5.79</v>
+        <v>5.59</v>
       </c>
       <c r="L153" t="n">
-        <v>5.74</v>
+        <v>5.59</v>
       </c>
       <c r="M153" t="n">
         <v>3</v>
       </c>
       <c r="N153" t="n">
-        <v>-0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="O153" t="n">
-        <v>0.553</v>
+        <v>0.526</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -18221,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X153" t="n">
         <v>0</v>
@@ -18233,21 +18207,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ebosse</t>
+          <t>Lazzari</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>5</v>
@@ -18261,45 +18235,45 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>5.75</v>
+        <v>5.79</v>
       </c>
       <c r="L154" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="M154" t="n">
         <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>2.44</v>
+        <v>-0.13</v>
       </c>
       <c r="O154" t="n">
-        <v>0.158</v>
+        <v>0.553</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -18308,7 +18282,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X154" t="n">
         <v>0</v>
@@ -18320,21 +18294,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sabelli</t>
+          <t>Ebosse</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
         <v>5</v>
@@ -18356,37 +18330,37 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K155" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="L155" t="n">
-        <v>5.65</v>
+        <v>5.72</v>
       </c>
       <c r="M155" t="n">
         <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>-0.24</v>
+        <v>2.44</v>
       </c>
       <c r="O155" t="n">
-        <v>0.649</v>
+        <v>0.158</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T155" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -18395,7 +18369,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -18407,24 +18381,24 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Marianucci</t>
+          <t>Sabelli</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F156" t="n">
         <v>2</v>
@@ -18435,45 +18409,45 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>25.8</v>
+        <v>28.2</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K156" t="n">
-        <v>5.73</v>
+        <v>5.81</v>
       </c>
       <c r="L156" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="O156" t="n">
-        <v>0.316</v>
+        <v>0.649</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -18482,7 +18456,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -18494,7 +18468,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Rugani</t>
+          <t>Marianucci</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18504,7 +18478,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -18522,7 +18496,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -18530,28 +18504,28 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K157" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
       <c r="L157" t="n">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
       <c r="M157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N157" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>0.193</v>
+        <v>0.316</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -18581,7 +18555,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ziolkowski</t>
+          <t>Rugani</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18591,17 +18565,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D158" t="n">
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
@@ -18609,28 +18583,30 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>21.3</v>
+        <v>25.3</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K158" t="n">
-        <v>5.94</v>
+        <v>5.69</v>
       </c>
       <c r="L158" t="n">
-        <v>5.78</v>
+        <v>5.56</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
-      </c>
-      <c r="N158" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N158" t="n">
+        <v>3.14</v>
+      </c>
       <c r="O158" t="n">
-        <v>0.237</v>
+        <v>0.193</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -18654,7 +18630,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X158" t="n">
         <v>0</v>
@@ -18666,27 +18642,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Candè</t>
+          <t>Ziolkowski</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
@@ -18694,7 +18670,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>18.8</v>
+        <v>21.3</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -18702,22 +18678,20 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K159" t="n">
-        <v>5.69</v>
+        <v>5.94</v>
       </c>
       <c r="L159" t="n">
-        <v>5.56</v>
+        <v>5.78</v>
       </c>
       <c r="M159" t="n">
-        <v>2</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-0.26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>0.329</v>
+        <v>0.237</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -18741,7 +18715,7 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X159" t="n">
         <v>0</v>
@@ -18753,27 +18727,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>Candè</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
@@ -18781,7 +18755,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -18789,22 +18763,22 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K160" t="n">
-        <v>5.65</v>
+        <v>5.69</v>
       </c>
       <c r="L160" t="n">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="M160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
-        <v>0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="O160" t="n">
-        <v>0.386</v>
+        <v>0.329</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -18828,7 +18802,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X160" t="n">
         <v>0</v>
@@ -18840,7 +18814,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Casale</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -18850,14 +18824,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
         <v>2</v>
@@ -18868,7 +18842,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -18876,22 +18850,22 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K161" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="L161" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N161" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="O161" t="n">
-        <v>0.303</v>
+        <v>0.386</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -18915,7 +18889,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -18927,58 +18901,58 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Goglichidze</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
         <v>5</v>
       </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>6</v>
-      </c>
       <c r="K162" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="L162" t="n">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
-        <v>2.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O162" t="n">
-        <v>0.342</v>
+        <v>0.303</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -19002,7 +18976,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
@@ -19014,56 +18988,58 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Moreno M.</t>
+          <t>Goglichidze</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
+        <v>5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
         <v>6</v>
       </c>
-      <c r="F163" t="n">
-        <v>3</v>
-      </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
       <c r="K163" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="L163" t="n">
-        <v>5.67</v>
+        <v>5.58</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2.01</v>
+      </c>
       <c r="O163" t="n">
-        <v>0.079</v>
+        <v>0.342</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -19075,10 +19051,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19087,7 +19063,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X163" t="n">
         <v>0</v>
@@ -19099,27 +19075,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ndaba</t>
+          <t>Moreno M.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
@@ -19127,7 +19103,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -19135,20 +19111,20 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M164" t="n">
         <v>1</v>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -19160,10 +19136,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T164" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -19184,7 +19160,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>Ndaba</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -19194,14 +19170,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F165" t="n">
         <v>2</v>
@@ -19212,7 +19188,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -19220,22 +19196,20 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K165" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L165" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M165" t="n">
-        <v>3</v>
-      </c>
-      <c r="N165" t="n">
-        <v>2.44</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="n">
-        <v>0.061</v>
+        <v>0.237</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -19247,10 +19221,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -19271,56 +19245,58 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Odenthal</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
+        <v>3</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2</v>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" t="n">
         <v>6</v>
       </c>
-      <c r="F166" t="n">
-        <v>3</v>
-      </c>
-      <c r="G166" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
-        <v>11</v>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0</v>
-      </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M166" t="n">
-        <v>1</v>
-      </c>
-      <c r="N166" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2.44</v>
+      </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -19332,13 +19308,13 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -19356,7 +19332,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Odenthal</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -19366,17 +19342,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
@@ -19384,7 +19360,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -19392,46 +19368,44 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>1</v>
+      </c>
+      <c r="T167" t="n">
         <v>10</v>
       </c>
-      <c r="K167" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L167" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="M167" t="n">
-        <v>2</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="n">
-        <v>2</v>
-      </c>
-      <c r="T167" t="n">
-        <v>5</v>
-      </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
@@ -19443,24 +19417,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sagrado</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F168" t="n">
         <v>2</v>
@@ -19471,7 +19445,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -19479,20 +19453,22 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K168" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L168" t="n">
-        <v>5.33</v>
+        <v>5.35</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
-      </c>
-      <c r="N168" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.68</v>
+      </c>
       <c r="O168" t="n">
-        <v>0.079</v>
+        <v>0.171</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -19507,10 +19483,10 @@
         <v>2</v>
       </c>
       <c r="T168" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="U168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -19528,21 +19504,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kofler</t>
+          <t>Sagrado</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E169" t="n">
         <v>4</v>
@@ -19555,33 +19531,57 @@
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L169" t="n">
+        <v>5.33</v>
+      </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
+      <c r="O169" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
       <c r="S169" t="n">
         <v>2</v>
       </c>
       <c r="T169" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
       </c>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
+      <c r="W169" t="n">
+        <v>1</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr"/>
@@ -19589,21 +19589,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Kofler</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E170" t="n">
         <v>4</v>
@@ -19630,7 +19630,7 @@
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T170" t="n">
         <v>6</v>
@@ -19650,24 +19650,24 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Terzic</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>4</v>
       </c>
       <c r="E171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F171" t="n">
         <v>2</v>
@@ -19691,10 +19691,10 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T171" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -19711,7 +19711,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Terzic</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19721,17 +19721,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
@@ -19752,10 +19752,10 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U172" t="n">
         <v>0</v>
@@ -19772,7 +19772,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19782,17 +19782,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
@@ -19813,10 +19813,10 @@
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T173" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19833,17 +19833,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -19874,10 +19874,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T174" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -19894,27 +19894,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
@@ -19935,10 +19935,10 @@
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -19955,27 +19955,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
@@ -19996,10 +19996,10 @@
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T176" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20016,12 +20016,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20033,10 +20033,10 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>2</v>
       </c>
       <c r="T177" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="U177" t="n">
         <v>0</v>
@@ -20077,17 +20077,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Tchato</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -20118,10 +20118,10 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T178" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U178" t="n">
         <v>0</v>
@@ -20138,27 +20138,27 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Tchato</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
@@ -20199,24 +20199,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F180" t="n">
         <v>2</v>
@@ -20260,24 +20260,24 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D181" t="n">
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F181" t="n">
         <v>2</v>
@@ -20321,68 +20321,46 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Dembelè A.</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H182" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J182" t="n">
-        <v>1</v>
-      </c>
-      <c r="K182" t="n">
-        <v>5</v>
-      </c>
-      <c r="L182" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="n">
-        <v>2</v>
-      </c>
-      <c r="N182" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
         <v>0</v>
       </c>
@@ -20395,12 +20373,8 @@
       <c r="V182" t="n">
         <v>0</v>
       </c>
-      <c r="W182" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" t="n">
-        <v>0</v>
-      </c>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
@@ -20408,24 +20382,24 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Patric</t>
+          <t>Dembelè A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D183" t="n">
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -20436,7 +20410,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>38.1</v>
+        <v>43.8</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -20444,22 +20418,22 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K183" t="n">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="L183" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="M183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.28</v>
+        <v>-0.89</v>
       </c>
       <c r="O183" t="n">
-        <v>0.325</v>
+        <v>0.132</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -20483,7 +20457,7 @@
         <v>0</v>
       </c>
       <c r="W183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X183" t="n">
         <v>0</v>
@@ -20495,17 +20469,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Goldaniga</t>
+          <t>Patric</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -20523,7 +20497,7 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>27.1</v>
+        <v>38.1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -20531,22 +20505,22 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M184" t="n">
         <v>3</v>
       </c>
       <c r="N184" t="n">
-        <v>-5.66</v>
+        <v>-0.28</v>
       </c>
       <c r="O184" t="n">
-        <v>0.377</v>
+        <v>0.325</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -20570,7 +20544,7 @@
         <v>0</v>
       </c>
       <c r="W184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X184" t="n">
         <v>0</v>
@@ -20582,7 +20556,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Amey</t>
+          <t>Goldaniga</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -20592,7 +20566,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -20610,11 +20584,11 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>11</v>
+        <v>27.1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -20627,11 +20601,13 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>1</v>
-      </c>
-      <c r="N185" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N185" t="n">
+        <v>-5.66</v>
+      </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -20667,7 +20643,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Antov</t>
+          <t>Amey</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -20677,14 +20653,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -20752,24 +20728,24 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Pieragnolo</t>
+          <t>Antov</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D187" t="n">
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
         <v>1</v>
@@ -20837,21 +20813,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Drobnic</t>
+          <t>Pieragnolo</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -20864,24 +20840,44 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="H188" t="n">
+        <v>11</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
       <c r="S188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -20889,8 +20885,12 @@
       <c r="V188" t="n">
         <v>0</v>
       </c>
-      <c r="W188" t="inlineStr"/>
-      <c r="X188" t="inlineStr"/>
+      <c r="W188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" t="n">
+        <v>0</v>
+      </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="inlineStr"/>
       <c r="AA188" t="inlineStr"/>
@@ -20898,21 +20898,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Drobnic</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
         <v>1</v>
@@ -20939,10 +20939,10 @@
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
@@ -20959,17 +20959,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Omar Fayed</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -21020,17 +21020,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Maye</t>
+          <t>Omar Fayed</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -21078,8 +21078,69 @@
       <c r="Z191" t="inlineStr"/>
       <c r="AA191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Maye</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Ds;Dc</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA191"/>
+  <autoFilter ref="A1:AA192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Attaccanti" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA64"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1050,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Butez</t>
+          <t>Milinkovic-Savic V.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
         <v>13</v>
       </c>
-      <c r="E7" t="n">
-        <v>43</v>
-      </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>79.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>5.37</v>
+        <v>5.65</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="O7" t="n">
-        <v>0.737</v>
+        <v>0.877</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>4.62</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>De Gea</t>
+          <t>Butez</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>71.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1173,37 +1173,37 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>6.24</v>
+        <v>6.07</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>5.37</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0.947</v>
+        <v>0.737</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>4.62</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meret</t>
+          <t>De Gea</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1234,17 +1234,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -1252,45 +1252,45 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="L9" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.25</v>
+        <v>-0.41</v>
       </c>
       <c r="O9" t="n">
-        <v>0.667</v>
+        <v>0.947</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>4.67</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Falcone</t>
+          <t>Meret</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1321,75 +1321,75 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>12</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>38</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>50</v>
-      </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mandas</t>
+          <t>Falcone</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -1426,30 +1426,30 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>68.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.5</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>0.149</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skorupski</t>
+          <t>Mandas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -1513,30 +1513,30 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.13</v>
+        <v>-5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0.675</v>
+        <v>0.149</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>4.38</v>
+        <v>6.6</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Caprile</t>
+          <t>Skorupski</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1582,72 +1582,72 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>15</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>1a Fascia</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>38</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>53</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okoye</t>
+          <t>Caprile</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>6.07</v>
+        <v>6.29</v>
       </c>
       <c r="L14" t="n">
-        <v>5.08</v>
+        <v>4.87</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="O14" t="n">
-        <v>0.667</v>
+        <v>0.728</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Palmisani</t>
+          <t>Okoye</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1756,17 +1756,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>30.8</v>
+        <v>58.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1782,26 +1782,28 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.48</v>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1810,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1819,10 +1821,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
@@ -1831,7 +1833,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Perri</t>
+          <t>Palmisani</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1841,41 +1843,61 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1a Fascia</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>6.1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1883,8 +1905,12 @@
       <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -1892,7 +1918,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Milinkovic-Savic V.</t>
+          <t>Perri</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1902,63 +1928,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>2a Fascia</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>27</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5.65</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1a Fascia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1966,12 +1970,8 @@
       <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" t="n">
-        <v>24</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sanchez Ro.</t>
+          <t>Lezzerini</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2938,41 +2938,61 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>2a Fascia</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2980,8 +3000,12 @@
       <c r="V29" t="n">
         <v>0</v>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -2989,7 +3013,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daffara</t>
+          <t>Sanchez Ro.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2999,17 +3023,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
@@ -3030,10 +3054,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3050,7 +3074,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thiam</t>
+          <t>Daffara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3060,17 +3084,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -3091,10 +3115,10 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3111,7 +3135,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Happonen</t>
+          <t>Thiam</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3121,17 +3145,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
@@ -3152,10 +3176,10 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3172,7 +3196,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Terracciano</t>
+          <t>Happonen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3182,7 +3206,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3194,46 +3218,24 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>6</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6</v>
-      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2a Fascia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
         <v>0</v>
       </c>
@@ -3246,12 +3248,8 @@
       <c r="V33" t="n">
         <v>0</v>
       </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -3259,7 +3257,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Motta</t>
+          <t>Terracciano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3269,7 +3267,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -3287,7 +3285,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>62.8</v>
+        <v>73.7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3295,20 +3293,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>5.17</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O34" t="n">
-        <v>0.237</v>
+        <v>0.333</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3332,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Turati</t>
+          <t>Motta</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>53.2</v>
+        <v>62.8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3380,22 +3380,20 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" t="n">
         <v>6</v>
       </c>
-      <c r="K35" t="n">
-        <v>6.17</v>
-      </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0.588</v>
+        <v>0.237</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3419,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
@@ -3431,7 +3429,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pinsoglio</t>
+          <t>Turati</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3441,7 +3439,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -3459,30 +3457,30 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>41.4</v>
+        <v>53.2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M36" t="n">
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>-2.44</v>
+        <v>0.37</v>
       </c>
       <c r="O36" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3506,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3518,7 +3516,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Contini</t>
+          <t>Padelli</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3528,7 +3526,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -3546,30 +3544,30 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>40.5</v>
+        <v>47.6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M37" t="n">
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.25</v>
+        <v>1.19</v>
       </c>
       <c r="O37" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3593,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3605,7 +3603,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Di Gennaro</t>
+          <t>Pinsoglio</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,7 +3613,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -3633,7 +3631,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>40</v>
+        <v>41.4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3641,22 +3639,22 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.56</v>
+        <v>-2.44</v>
       </c>
       <c r="O38" t="n">
-        <v>0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3680,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3692,7 +3690,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gollini</t>
+          <t>Contini</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3702,7 +3700,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -3720,7 +3718,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>39.1</v>
+        <v>40.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3740,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>-4.37</v>
+        <v>-2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0.123</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3779,7 +3777,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lezzerini</t>
+          <t>Di Gennaro</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3789,7 +3787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -3807,7 +3805,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3815,20 +3813,22 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.56</v>
+      </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Stolz</t>
+          <t>Gollini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>30.8</v>
+        <v>39.1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3909,13 +3909,13 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>-4.37</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Torriani</t>
+          <t>Stolz</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4038,7 +4038,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De Marzi</t>
+          <t>Torriani</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4083,9 +4083,11 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -4123,7 +4125,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Russo A.</t>
+          <t>De Marzi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4133,7 +4135,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4208,7 +4210,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Siviero</t>
+          <t>Russo A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4218,7 +4220,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4293,7 +4295,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sommariva</t>
+          <t>Siviero</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4303,7 +4305,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -4321,7 +4323,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4329,22 +4331,20 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4380,7 +4380,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Desplanches</t>
+          <t>Sommariva</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4407,19 +4407,41 @@
           <t>3a Fascia</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.75</v>
+      </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
@@ -4432,8 +4454,12 @@
       <c r="V47" t="n">
         <v>0</v>
       </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
@@ -4441,7 +4467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lolic</t>
+          <t>Desplanches</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4502,7 +4528,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Renzetti</t>
+          <t>Lolic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4512,7 +4538,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -4563,7 +4589,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Strajnar</t>
+          <t>Renzetti</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4573,7 +4599,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -4624,7 +4650,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mascardi</t>
+          <t>Strajnar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4634,7 +4660,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -4665,10 +4691,10 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4685,7 +4711,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Montipò</t>
+          <t>Mascardi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4695,7 +4721,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4707,51 +4733,29 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>35</v>
-      </c>
-      <c r="K52" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>4.94</v>
-      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4759,12 +4763,8 @@
       <c r="V52" t="n">
         <v>0</v>
       </c>
-      <c r="W52" t="n">
-        <v>54</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
@@ -4772,7 +4772,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Padelli</t>
+          <t>Montipò</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>47.6</v>
+        <v>62.4</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4808,28 +4808,28 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="L53" t="n">
-        <v>5.25</v>
+        <v>4.94</v>
       </c>
       <c r="M53" t="n">
         <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>1.19</v>
+        <v>0.29</v>
       </c>
       <c r="O53" t="n">
-        <v>0.026</v>
+        <v>0.947</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -5467,9 +5467,9 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -5625,8 +5625,69 @@
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Por</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA64"/>
+  <autoFilter ref="A1:AA65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5637,7 +5698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA192"/>
+  <dimension ref="A1:AA191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6183,7 +6244,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -6270,7 +6331,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -6505,7 +6566,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -6592,7 +6653,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -6679,7 +6740,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -6766,7 +6827,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -6853,7 +6914,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -6940,7 +7001,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7027,7 +7088,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7114,7 +7175,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7199,7 +7260,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -7286,7 +7347,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7373,7 +7434,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -7460,7 +7521,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -7547,7 +7608,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -7634,7 +7695,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -7721,7 +7782,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -7806,7 +7867,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -7893,7 +7954,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -7980,7 +8041,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>64</v>
+        <v>63.7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8067,7 +8128,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8154,7 +8215,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -8241,7 +8302,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -8659,7 +8720,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>88.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -8746,7 +8807,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -8833,7 +8894,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -8918,7 +8979,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>75.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -9003,7 +9064,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>74.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9090,7 +9151,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>73.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9177,7 +9238,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9264,7 +9325,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -9349,7 +9410,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -9436,7 +9497,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -9523,7 +9584,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>68.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -9610,7 +9671,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -9697,7 +9758,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -9784,7 +9845,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -9871,7 +9932,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -9956,7 +10017,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -10043,7 +10104,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10130,7 +10191,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10217,7 +10278,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10302,7 +10363,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10389,7 +10450,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -10476,7 +10537,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -10563,7 +10624,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10650,7 +10711,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10737,7 +10798,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10824,7 +10885,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10881,21 +10942,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Fortini</t>
+          <t>Marcandalli</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
         <v>12</v>
@@ -10909,7 +10970,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10917,26 +10978,28 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K62" t="n">
-        <v>5.96</v>
+        <v>5.87</v>
       </c>
       <c r="L62" t="n">
-        <v>5.96</v>
+        <v>5.84</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.09</v>
+      </c>
       <c r="O62" t="n">
-        <v>0.316</v>
+        <v>0.513</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -10945,7 +11008,7 @@
         <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -10954,7 +11017,7 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -10966,21 +11029,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marcandalli</t>
+          <t>Fortini</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
         <v>12</v>
@@ -10994,7 +11057,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -11002,28 +11065,26 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>5.87</v>
+        <v>5.96</v>
       </c>
       <c r="L63" t="n">
-        <v>5.84</v>
+        <v>5.96</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0.09</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>0.513</v>
+        <v>0.316</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -11032,7 +11093,7 @@
         <v>5</v>
       </c>
       <c r="T63" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -11041,7 +11102,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -11081,7 +11142,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -11166,7 +11227,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -11253,7 +11314,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -11423,7 +11484,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -11765,7 +11826,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -12754,7 +12815,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -12841,7 +12902,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -12928,7 +12989,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -13013,7 +13074,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -13098,7 +13159,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -13185,7 +13246,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -13272,7 +13333,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -13359,7 +13420,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -13446,7 +13507,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -13533,7 +13594,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -13620,7 +13681,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -13707,7 +13768,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -13794,7 +13855,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>56.8</v>
+        <v>56.5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -13881,7 +13942,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -13966,7 +14027,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -14053,7 +14114,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -14112,24 +14173,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tomori</t>
+          <t>Haps</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F103" t="n">
         <v>4</v>
@@ -14140,7 +14201,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>55.3</v>
+        <v>54.3</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -14148,25 +14209,25 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K103" t="n">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="L103" t="n">
-        <v>5.88</v>
+        <v>5.98</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="O103" t="n">
-        <v>0.658</v>
+        <v>0.474</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
@@ -14175,22 +14236,22 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
@@ -14199,27 +14260,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Haps</t>
+          <t>Kossounou</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
@@ -14227,36 +14288,36 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>54.6</v>
+        <v>51.9</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K104" t="n">
-        <v>5.86</v>
+        <v>5.94</v>
       </c>
       <c r="L104" t="n">
-        <v>5.98</v>
+        <v>6.09</v>
       </c>
       <c r="M104" t="n">
         <v>2</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.02</v>
+        <v>0.18</v>
       </c>
       <c r="O104" t="n">
-        <v>0.474</v>
+        <v>0.434</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -14265,16 +14326,16 @@
         <v>4</v>
       </c>
       <c r="T104" t="n">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -14286,12 +14347,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kossounou</t>
+          <t>Kolasinac</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14300,10 +14361,10 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F105" t="n">
         <v>6</v>
@@ -14314,7 +14375,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>52.2</v>
+        <v>45.3</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -14322,25 +14383,25 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K105" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L105" t="n">
         <v>5.94</v>
       </c>
-      <c r="L105" t="n">
-        <v>6.09</v>
-      </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N105" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O105" t="n">
-        <v>0.434</v>
+        <v>0.605</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -14352,7 +14413,7 @@
         <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -14361,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -14373,27 +14434,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kolasinac</t>
+          <t>Comuzzo</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
@@ -14401,7 +14462,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>45.5</v>
+        <v>43.8</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -14409,25 +14470,25 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K106" t="n">
-        <v>6.03</v>
+        <v>5.75</v>
       </c>
       <c r="L106" t="n">
-        <v>5.94</v>
+        <v>5.75</v>
       </c>
       <c r="M106" t="n">
         <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="O106" t="n">
-        <v>0.605</v>
+        <v>0.474</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -14439,16 +14500,16 @@
         <v>4</v>
       </c>
       <c r="T106" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -14460,27 +14521,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Comuzzo</t>
+          <t>Bertola</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;Dc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
@@ -14488,54 +14549,52 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K107" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="n">
         <v>5.75</v>
       </c>
-      <c r="L107" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M107" t="n">
-        <v>3</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="P107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>4</v>
-      </c>
-      <c r="T107" t="n">
-        <v>6.75</v>
-      </c>
       <c r="U107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -14547,17 +14606,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bertola</t>
+          <t>Carboni A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dd;Ds;Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -14575,7 +14634,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -14583,35 +14642,37 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K108" t="n">
-        <v>5.86</v>
+        <v>5.63</v>
       </c>
       <c r="L108" t="n">
-        <v>5.84</v>
+        <v>5.62</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
-      </c>
-      <c r="N108" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-0.38</v>
+      </c>
       <c r="O108" t="n">
-        <v>0.658</v>
+        <v>0.618</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T108" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -14620,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X108" t="n">
         <v>0</v>
@@ -14632,27 +14693,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Carboni A.</t>
+          <t>Hien</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
@@ -14660,45 +14721,45 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K109" t="n">
-        <v>5.63</v>
+        <v>5.91</v>
       </c>
       <c r="L109" t="n">
-        <v>5.62</v>
+        <v>5.86</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.38</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O109" t="n">
-        <v>0.618</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -14719,21 +14780,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hien</t>
+          <t>Olivera</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E110" t="n">
         <v>10</v>
@@ -14747,7 +14808,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>43</v>
+        <v>39.6</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -14755,25 +14816,25 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K110" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="L110" t="n">
-        <v>5.86</v>
+        <v>5.68</v>
       </c>
       <c r="M110" t="n">
         <v>3</v>
       </c>
       <c r="N110" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="O110" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="P110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -14782,10 +14843,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -14794,7 +14855,7 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X110" t="n">
         <v>0</v>
@@ -14806,21 +14867,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Olivera</t>
+          <t>Valenti</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
         <v>10</v>
@@ -14834,7 +14895,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -14842,22 +14903,22 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K111" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="L111" t="n">
-        <v>5.68</v>
+        <v>5.83</v>
       </c>
       <c r="M111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N111" t="n">
-        <v>-0.31</v>
+        <v>-0.02</v>
       </c>
       <c r="O111" t="n">
-        <v>0.649</v>
+        <v>0.618</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -14869,10 +14930,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -14881,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X111" t="n">
         <v>0</v>
@@ -14893,7 +14954,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Valenti</t>
+          <t>Siebert</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -14903,63 +14964,61 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>19</v>
+      </c>
+      <c r="K112" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L112" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
         <v>5</v>
       </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>27</v>
-      </c>
-      <c r="K112" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="L112" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="M112" t="n">
-        <v>2</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>1</v>
-      </c>
       <c r="T112" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -14968,7 +15027,7 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X112" t="n">
         <v>0</v>
@@ -14980,7 +15039,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Siebert</t>
+          <t>Provstgaard</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -14990,11 +15049,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E113" t="n">
         <v>12</v>
@@ -15008,7 +15067,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -15016,23 +15075,25 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K113" t="n">
-        <v>5.68</v>
+        <v>5.91</v>
       </c>
       <c r="L113" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
-      </c>
-      <c r="N113" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="O113" t="n">
-        <v>0.5</v>
+        <v>0.316</v>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -15044,7 +15105,7 @@
         <v>5</v>
       </c>
       <c r="T113" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -15065,21 +15126,21 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Provstgaard</t>
+          <t>Britschgi</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
         <v>12</v>
@@ -15093,7 +15154,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>36.7</v>
+        <v>35.9</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -15101,49 +15162,47 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K114" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="L114" t="n">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
-        <v>0.316</v>
+        <v>0.737</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
       <c r="S114" t="n">
+        <v>3</v>
+      </c>
+      <c r="T114" t="n">
+        <v>6</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
         <v>5</v>
       </c>
-      <c r="T114" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" t="n">
-        <v>3</v>
-      </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
@@ -15152,27 +15211,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Britschgi</t>
+          <t>Walukiewicz</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
@@ -15180,43 +15239,45 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K115" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="L115" t="n">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O115" t="n">
-        <v>0.737</v>
+        <v>0.781</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -15225,10 +15286,10 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
@@ -15237,73 +15298,71 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Walukiewicz</t>
+          <t>Floriani Mussolini</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
+        <v>6</v>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>23</v>
+      </c>
+      <c r="K116" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
         <v>5</v>
       </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>34</v>
-      </c>
-      <c r="K116" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="L116" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>1</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -15312,7 +15371,7 @@
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -15324,7 +15383,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Floriani Mussolini</t>
+          <t>Smolcic I.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15334,17 +15393,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
@@ -15352,7 +15411,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>34.2</v>
+        <v>33.4</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -15360,20 +15419,22 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K117" t="n">
-        <v>5.72</v>
+        <v>5.96</v>
       </c>
       <c r="L117" t="n">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
-      </c>
-      <c r="N117" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.09</v>
+      </c>
       <c r="O117" t="n">
-        <v>0.605</v>
+        <v>0.434</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -15385,10 +15446,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T117" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -15397,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -15409,21 +15470,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Smolcic I.</t>
+          <t>Mazzocchi</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>10</v>
@@ -15437,7 +15498,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -15445,22 +15506,22 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K118" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="L118" t="n">
-        <v>5.84</v>
+        <v>5.94</v>
       </c>
       <c r="M118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N118" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="O118" t="n">
-        <v>0.434</v>
+        <v>0.386</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -15472,10 +15533,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -15484,10 +15545,10 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
@@ -15496,27 +15557,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mazzocchi</t>
+          <t>Vitik</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
@@ -15524,7 +15585,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -15532,28 +15593,26 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K119" t="n">
         <v>5.94</v>
       </c>
       <c r="L119" t="n">
-        <v>5.94</v>
+        <v>5.86</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0.29</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>0.386</v>
+        <v>0.474</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -15571,10 +15630,10 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
@@ -15583,7 +15642,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vitik</t>
+          <t>Ghilardi</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15593,11 +15652,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E120" t="n">
         <v>9</v>
@@ -15611,7 +15670,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -15619,20 +15678,22 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K120" t="n">
-        <v>5.94</v>
+        <v>5.98</v>
       </c>
       <c r="L120" t="n">
-        <v>5.86</v>
+        <v>5.95</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
-      </c>
-      <c r="N120" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.41</v>
+      </c>
       <c r="O120" t="n">
-        <v>0.474</v>
+        <v>0.592</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -15644,10 +15705,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -15656,7 +15717,7 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15668,7 +15729,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ghilardi</t>
+          <t>Gaspar K.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15678,17 +15739,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E121" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
@@ -15696,27 +15757,27 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>32.4</v>
+        <v>31</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J121" t="n">
         <v>21</v>
       </c>
       <c r="K121" t="n">
-        <v>5.98</v>
+        <v>5.83</v>
       </c>
       <c r="L121" t="n">
-        <v>5.95</v>
+        <v>5.64</v>
       </c>
       <c r="M121" t="n">
         <v>2</v>
       </c>
       <c r="N121" t="n">
-        <v>0.41</v>
+        <v>-0.51</v>
       </c>
       <c r="O121" t="n">
         <v>0.592</v>
@@ -15731,22 +15792,22 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T121" t="n">
+        <v>5</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
         <v>6</v>
       </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>1</v>
-      </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
@@ -15755,7 +15816,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Gaspar K.</t>
+          <t>Pongracic</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15765,48 +15826,48 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>8</v>
+      </c>
+      <c r="F122" t="n">
         <v>4</v>
       </c>
-      <c r="E122" t="n">
-        <v>12</v>
-      </c>
-      <c r="F122" t="n">
-        <v>6</v>
-      </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
           <t>3a Fascia</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>31</v>
+        <v>29.1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K122" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="L122" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="M122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.51</v>
+        <v>-0.04</v>
       </c>
       <c r="O122" t="n">
-        <v>0.592</v>
+        <v>0.772</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -15818,7 +15879,7 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T122" t="n">
         <v>5</v>
@@ -15830,10 +15891,10 @@
         <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
@@ -15842,82 +15903,80 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Pongracic</t>
+          <t>Oyono A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>14</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="L123" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>1</v>
+      </c>
+      <c r="W123" t="n">
         <v>4</v>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H123" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>35</v>
-      </c>
-      <c r="K123" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="L123" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M123" t="n">
-        <v>3</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" t="n">
-        <v>5</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>12</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -15929,80 +15988,80 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Oyono A.</t>
+          <t>Arizala</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
         <v>5</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>14</v>
-      </c>
       <c r="K124" t="n">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="L124" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>0.368</v>
+        <v>0.132</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X124" t="n">
         <v>0</v>
@@ -16014,27 +16073,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Arizala</t>
+          <t>Bella-Kotchap</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
@@ -16042,28 +16101,28 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>25.6</v>
+        <v>24.9</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K125" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="L125" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="M125" t="n">
         <v>1</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
-        <v>0.132</v>
+        <v>0.474</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -16075,10 +16134,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -16087,7 +16146,7 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
@@ -16099,12 +16158,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bella-Kotchap</t>
+          <t>Juan Jesus</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -16116,10 +16175,10 @@
         <v>4</v>
       </c>
       <c r="E126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -16127,28 +16186,30 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K126" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="L126" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="M126" t="n">
-        <v>1</v>
-      </c>
-      <c r="N126" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="O126" t="n">
-        <v>0.474</v>
+        <v>0.509</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -16163,7 +16224,7 @@
         <v>2</v>
       </c>
       <c r="T126" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -16172,10 +16233,10 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
@@ -16184,73 +16245,71 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Juan Jesus</t>
+          <t>Cittadini</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>4</v>
       </c>
       <c r="E127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F127" t="n">
+        <v>6</v>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>24</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Trappola</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>6</v>
+      </c>
+      <c r="L127" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
         <v>5</v>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>21</v>
-      </c>
-      <c r="K127" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="L127" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="M127" t="n">
-        <v>3</v>
-      </c>
-      <c r="N127" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>2</v>
-      </c>
       <c r="T127" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -16259,10 +16318,10 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
@@ -16271,7 +16330,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cittadini</t>
+          <t>Schingtienne</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16281,17 +16340,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
@@ -16299,7 +16358,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>23.9</v>
+        <v>16.9</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -16307,20 +16366,20 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K128" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L128" t="n">
-        <v>5.83</v>
+        <v>5.63</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>0.079</v>
+        <v>0.395</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -16335,7 +16394,7 @@
         <v>5</v>
       </c>
       <c r="T128" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16344,7 +16403,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X128" t="n">
         <v>0</v>
@@ -16356,7 +16415,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Schingtienne</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -16366,17 +16425,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
@@ -16384,28 +16443,28 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>17</v>
+        <v>14.9</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Trappola</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K129" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L129" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="M129" t="n">
         <v>1</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>0.395</v>
+        <v>0.105</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -16417,10 +16476,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -16429,7 +16488,7 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -16441,7 +16500,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Ndiaye</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16451,11 +16510,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>8</v>
@@ -16469,7 +16528,7 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>14.9</v>
+        <v>11.6</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -16477,20 +16536,20 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
       <c r="L130" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="M130" t="n">
         <v>1</v>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>0.105</v>
+        <v>0.289</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -16505,7 +16564,7 @@
         <v>1</v>
       </c>
       <c r="T130" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -16514,10 +16573,10 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
@@ -16526,7 +16585,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ndiaye</t>
+          <t>Lucchesi</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -16536,17 +16595,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E131" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F131" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
@@ -16554,28 +16613,28 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Trappola</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
         <v>1</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="n">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -16587,10 +16646,10 @@
         <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T131" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -16599,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
@@ -16611,7 +16670,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lucchesi</t>
+          <t>Koulierakis</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -16621,74 +16680,50 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D132" t="n">
+        <v>7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>9</v>
+      </c>
+      <c r="F132" t="n">
         <v>4</v>
       </c>
-      <c r="E132" t="n">
-        <v>12</v>
-      </c>
-      <c r="F132" t="n">
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
         <v>6</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
-        <v>11</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Trappola</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>1</v>
-      </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>5</v>
-      </c>
-      <c r="T132" t="n">
-        <v>5.5</v>
-      </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
       </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
@@ -16696,24 +16731,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Koulierakis</t>
+          <t>Correia T.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -16737,7 +16772,7 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T133" t="n">
         <v>6</v>
@@ -16757,17 +16792,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Correia T.</t>
+          <t>Badiashile</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -16798,10 +16833,10 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -16818,7 +16853,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Badiashile</t>
+          <t>Caleta-Car</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -16828,17 +16863,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D135" t="n">
         <v>6</v>
       </c>
       <c r="E135" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
@@ -16862,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="T135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -16879,27 +16914,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Caleta-Car</t>
+          <t>Sugawara</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -16920,7 +16955,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T136" t="n">
         <v>6</v>
@@ -16940,27 +16975,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sugawara</t>
+          <t>Leite</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>6</v>
       </c>
       <c r="E137" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
@@ -16981,10 +17016,10 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -17001,27 +17036,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Leite</t>
+          <t>Valdepenas</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
@@ -17042,10 +17077,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -17062,27 +17097,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Valdepenas</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>5</v>
       </c>
       <c r="E139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -17103,10 +17138,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T139" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -17123,17 +17158,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Cinquegrano</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -17164,16 +17199,16 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T140" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
@@ -17184,7 +17219,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cinquegrano</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -17194,17 +17229,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>5</v>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -17225,16 +17260,16 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -17245,21 +17280,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Lulli</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E142" t="n">
         <v>10</v>
@@ -17286,10 +17321,10 @@
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T142" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -17306,27 +17341,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lulli</t>
+          <t>Drameh</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
@@ -17347,10 +17382,10 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -17367,46 +17402,68 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Drameh</t>
+          <t>Beukema</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F144" t="n">
         <v>4</v>
       </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>3a Fascia</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>22</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="L144" t="n">
+        <v>6.16</v>
+      </c>
       <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="P144" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
       <c r="S144" t="n">
         <v>0</v>
       </c>
@@ -17419,8 +17476,12 @@
       <c r="V144" t="n">
         <v>0</v>
       </c>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
+      <c r="W144" t="n">
+        <v>2</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
@@ -17428,27 +17489,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Beukema</t>
+          <t>Cabal</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
         <v>4</v>
       </c>
-      <c r="E145" t="n">
-        <v>7</v>
-      </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
@@ -17456,7 +17517,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>67.3</v>
+        <v>65.2</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -17464,22 +17525,22 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K145" t="n">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="L145" t="n">
-        <v>6.16</v>
+        <v>6.56</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="O145" t="n">
-        <v>0.754</v>
+        <v>0.298</v>
       </c>
       <c r="P145" t="n">
         <v>2</v>
@@ -17503,7 +17564,7 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17515,24 +17576,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Cabal</t>
+          <t>Idrissi R.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
@@ -17543,7 +17604,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>65.2</v>
+        <v>62</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -17551,22 +17612,20 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K146" t="n">
-        <v>5.94</v>
+        <v>5.82</v>
       </c>
       <c r="L146" t="n">
-        <v>6.56</v>
+        <v>6.09</v>
       </c>
       <c r="M146" t="n">
-        <v>3</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0.53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="n">
-        <v>0.298</v>
+        <v>0.447</v>
       </c>
       <c r="P146" t="n">
         <v>2</v>
@@ -17590,7 +17649,7 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17602,27 +17661,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Idrissi R.</t>
+          <t>Tomori</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E147" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
@@ -17630,7 +17689,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>62.3</v>
+        <v>55.1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -17638,26 +17697,28 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K147" t="n">
-        <v>5.82</v>
+        <v>5.97</v>
       </c>
       <c r="L147" t="n">
-        <v>6.09</v>
+        <v>5.88</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
-      </c>
-      <c r="N147" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-0.12</v>
+      </c>
       <c r="O147" t="n">
-        <v>0.447</v>
+        <v>0.658</v>
       </c>
       <c r="P147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -17675,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
@@ -17715,7 +17776,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -17802,7 +17863,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -17889,7 +17950,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -17976,7 +18037,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -18294,21 +18355,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ebosse</t>
+          <t>Sabelli</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>5</v>
@@ -18326,42 +18387,42 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K155" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="L155" t="n">
-        <v>5.72</v>
+        <v>5.65</v>
       </c>
       <c r="M155" t="n">
         <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>2.44</v>
+        <v>-0.24</v>
       </c>
       <c r="O155" t="n">
-        <v>0.158</v>
+        <v>0.649</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
       <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
         <v>5</v>
       </c>
-      <c r="T155" t="n">
-        <v>5.6</v>
-      </c>
       <c r="U155" t="n">
         <v>0</v>
       </c>
@@ -18369,7 +18430,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -18381,21 +18442,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sabelli</t>
+          <t>Ebosse</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
         <v>5</v>
@@ -18409,45 +18470,45 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K156" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="L156" t="n">
-        <v>5.65</v>
+        <v>5.72</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>-0.24</v>
+        <v>2.44</v>
       </c>
       <c r="O156" t="n">
-        <v>0.649</v>
+        <v>0.158</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T156" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -18456,7 +18517,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -18583,7 +18644,7 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -18670,7 +18731,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -18755,7 +18816,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -18842,7 +18903,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -18929,7 +18990,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -19016,7 +19077,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -19103,7 +19164,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -19245,27 +19306,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>Odenthal</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
@@ -19273,7 +19334,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -19281,22 +19342,20 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3</v>
-      </c>
-      <c r="N166" t="n">
-        <v>2.44</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -19308,13 +19367,13 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -19332,7 +19391,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Odenthal</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -19342,17 +19401,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
@@ -19368,20 +19427,22 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="M167" t="n">
-        <v>1</v>
-      </c>
-      <c r="N167" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0.68</v>
+      </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -19393,19 +19454,19 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T167" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
@@ -19417,24 +19478,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Sagrado</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F168" t="n">
         <v>2</v>
@@ -19445,7 +19506,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -19453,22 +19514,20 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K168" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L168" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="M168" t="n">
-        <v>2</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0.68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="n">
-        <v>0.171</v>
+        <v>0.079</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -19483,10 +19542,10 @@
         <v>2</v>
       </c>
       <c r="T168" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="U168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -19504,21 +19563,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sagrado</t>
+          <t>Kofler</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E169" t="n">
         <v>4</v>
@@ -19531,57 +19590,33 @@
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H169" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L169" t="n">
-        <v>5.33</v>
-      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
       <c r="S169" t="n">
         <v>2</v>
       </c>
       <c r="T169" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="U169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
       </c>
-      <c r="W169" t="n">
-        <v>1</v>
-      </c>
-      <c r="X169" t="n">
-        <v>0</v>
-      </c>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr"/>
@@ -19589,21 +19624,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Kofler</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E170" t="n">
         <v>4</v>
@@ -19630,7 +19665,7 @@
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T170" t="n">
         <v>6</v>
@@ -19650,24 +19685,24 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Terzic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>4</v>
       </c>
       <c r="E171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F171" t="n">
         <v>2</v>
@@ -19691,10 +19726,10 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T171" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -19711,7 +19746,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Terzic</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19721,17 +19756,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D172" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" t="n">
+        <v>7</v>
+      </c>
+      <c r="F172" t="n">
         <v>4</v>
-      </c>
-      <c r="E172" t="n">
-        <v>5</v>
-      </c>
-      <c r="F172" t="n">
-        <v>2</v>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
@@ -19752,10 +19787,10 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T172" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U172" t="n">
         <v>0</v>
@@ -19772,7 +19807,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19782,17 +19817,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
@@ -19813,10 +19848,10 @@
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19833,17 +19868,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -19874,10 +19909,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -19894,27 +19929,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
@@ -19935,10 +19970,10 @@
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -19955,27 +19990,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
@@ -19996,10 +20031,10 @@
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T176" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20016,12 +20051,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20033,10 +20068,10 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
@@ -20060,7 +20095,7 @@
         <v>2</v>
       </c>
       <c r="T177" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="U177" t="n">
         <v>0</v>
@@ -20077,17 +20112,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Tchato</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -20118,10 +20153,10 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T178" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="U178" t="n">
         <v>0</v>
@@ -20138,27 +20173,27 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Tchato</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
@@ -20199,24 +20234,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F180" t="n">
         <v>2</v>
@@ -20260,24 +20295,24 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D181" t="n">
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F181" t="n">
         <v>2</v>
@@ -20321,46 +20356,68 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Dembelè A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Affare</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="n">
         <v>5</v>
       </c>
-      <c r="F182" t="n">
-        <v>2</v>
-      </c>
-      <c r="G182" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
+      <c r="L182" t="n">
+        <v>5</v>
+      </c>
       <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N182" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
       <c r="S182" t="n">
         <v>0</v>
       </c>
@@ -20373,8 +20430,12 @@
       <c r="V182" t="n">
         <v>0</v>
       </c>
-      <c r="W182" t="inlineStr"/>
-      <c r="X182" t="inlineStr"/>
+      <c r="W182" t="n">
+        <v>0</v>
+      </c>
+      <c r="X182" t="n">
+        <v>0</v>
+      </c>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
@@ -20382,24 +20443,24 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Dembelè A.</t>
+          <t>Goldaniga</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D183" t="n">
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -20410,7 +20471,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>43.8</v>
+        <v>27</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -20418,22 +20479,22 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.89</v>
+        <v>-5.66</v>
       </c>
       <c r="O183" t="n">
-        <v>0.132</v>
+        <v>0.377</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -20469,27 +20530,27 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Patric</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
@@ -20497,30 +20558,30 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>38.1</v>
+        <v>14.2</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K184" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="L184" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="M184" t="n">
         <v>3</v>
       </c>
       <c r="N184" t="n">
-        <v>-0.28</v>
+        <v>2.44</v>
       </c>
       <c r="O184" t="n">
-        <v>0.325</v>
+        <v>0.061</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -20544,7 +20605,7 @@
         <v>0</v>
       </c>
       <c r="W184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X184" t="n">
         <v>0</v>
@@ -20556,7 +20617,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Goldaniga</t>
+          <t>Amey</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -20566,7 +20627,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -20584,11 +20645,11 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>27.1</v>
+        <v>11</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -20601,13 +20662,11 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3</v>
-      </c>
-      <c r="N185" t="n">
-        <v>-5.66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="n">
-        <v>0.377</v>
+        <v>0</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -20643,7 +20702,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Amey</t>
+          <t>Antov</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -20653,14 +20712,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -20728,24 +20787,24 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Antov</t>
+          <t>Pieragnolo</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D187" t="n">
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
         <v>1</v>
@@ -20813,21 +20872,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Pieragnolo</t>
+          <t>Drobnic</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -20840,44 +20899,24 @@
           <t>Scommessa</t>
         </is>
       </c>
-      <c r="H188" t="n">
-        <v>11</v>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J188" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" t="n">
-        <v>0</v>
-      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
       <c r="S188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -20885,12 +20924,8 @@
       <c r="V188" t="n">
         <v>0</v>
       </c>
-      <c r="W188" t="n">
-        <v>0</v>
-      </c>
-      <c r="X188" t="n">
-        <v>0</v>
-      </c>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="inlineStr"/>
       <c r="AA188" t="inlineStr"/>
@@ -20898,21 +20933,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Drobnic</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" t="n">
         <v>1</v>
@@ -20939,10 +20974,10 @@
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
@@ -20959,17 +20994,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Omar Fayed</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -21020,17 +21055,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Omar Fayed</t>
+          <t>Maye</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -21078,69 +21113,8 @@
       <c r="Z191" t="inlineStr"/>
       <c r="AA191" t="inlineStr"/>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Maye</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Ds;Dc</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" t="n">
-        <v>0</v>
-      </c>
-      <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr"/>
-      <c r="Y192" t="inlineStr"/>
-      <c r="Z192" t="inlineStr"/>
-      <c r="AA192" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AA192"/>
+  <autoFilter ref="A1:AA191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portieri'!$A$1:$AA$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Difensori'!$A$1:$AA$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Centrocampisti'!$A$1:$AA$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Attaccanti'!$A$1:$AA$88</definedName>
   </definedNames>
@@ -5698,7 +5698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA191"/>
+  <dimension ref="A1:AA192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17428,73 +17428,51 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Dodò</t>
+          <t>Mitaj</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F144" t="n">
-        <v>2</v>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>36</v>
-      </c>
-      <c r="K144" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="L144" t="n">
-        <v>6.03</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>3a Fascia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
-        <v>3</v>
-      </c>
-      <c r="N144" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="P144" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>2</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -17502,12 +17480,8 @@
       <c r="V144" t="n">
         <v>0</v>
       </c>
-      <c r="W144" t="n">
-        <v>7</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
@@ -17515,24 +17489,24 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cabal</t>
+          <t>Dodò</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F145" t="n">
         <v>2</v>
@@ -17543,7 +17517,7 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>65.2</v>
+        <v>68.3</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -17551,37 +17525,37 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K145" t="n">
-        <v>5.94</v>
+        <v>5.99</v>
       </c>
       <c r="L145" t="n">
-        <v>6.56</v>
+        <v>6.03</v>
       </c>
       <c r="M145" t="n">
         <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>0.53</v>
+        <v>-0.01</v>
       </c>
       <c r="O145" t="n">
-        <v>0.298</v>
+        <v>0.675</v>
       </c>
       <c r="P145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -17590,7 +17564,7 @@
         <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17602,24 +17576,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Idrissi R.</t>
+          <t>Cabal</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
@@ -17630,7 +17604,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>62</v>
+        <v>65.2</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -17638,20 +17612,22 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K146" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="L146" t="n">
-        <v>6.09</v>
+        <v>6.56</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
-      </c>
-      <c r="N146" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.53</v>
+      </c>
       <c r="O146" t="n">
-        <v>0.447</v>
+        <v>0.298</v>
       </c>
       <c r="P146" t="n">
         <v>2</v>
@@ -17675,7 +17651,7 @@
         <v>0</v>
       </c>
       <c r="W146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17687,17 +17663,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>De Silvestri</t>
+          <t>Idrissi R.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -17715,7 +17691,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>49.9</v>
+        <v>62</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -17723,25 +17699,23 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>6.05</v>
+        <v>5.82</v>
       </c>
       <c r="L147" t="n">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="M147" t="n">
-        <v>3</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-0.34</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="n">
-        <v>0.333</v>
+        <v>0.447</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -17750,10 +17724,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -17762,7 +17736,7 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -17774,24 +17748,24 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pellegrini Lu.</t>
+          <t>De Silvestri</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" t="n">
         <v>2</v>
@@ -17802,7 +17776,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>47.5</v>
+        <v>49.9</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -17810,25 +17784,25 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K148" t="n">
-        <v>5.85</v>
+        <v>6.05</v>
       </c>
       <c r="L148" t="n">
-        <v>5.81</v>
+        <v>5.95</v>
       </c>
       <c r="M148" t="n">
         <v>3</v>
       </c>
       <c r="N148" t="n">
-        <v>-0.17</v>
+        <v>-0.34</v>
       </c>
       <c r="O148" t="n">
-        <v>0.526</v>
+        <v>0.333</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -17837,10 +17811,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -17849,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -17861,27 +17835,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Van Der Brempt</t>
+          <t>Pellegrini Lu.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
@@ -17889,7 +17863,7 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>43.2</v>
+        <v>47.5</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -17897,28 +17871,28 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K149" t="n">
-        <v>5.96</v>
+        <v>5.85</v>
       </c>
       <c r="L149" t="n">
-        <v>5.96</v>
+        <v>5.81</v>
       </c>
       <c r="M149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="O149" t="n">
-        <v>0.421</v>
+        <v>0.526</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -17936,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -17948,27 +17922,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sverko</t>
+          <t>Van Der Brempt</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
@@ -17976,7 +17950,7 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -17987,23 +17961,25 @@
         <v>14</v>
       </c>
       <c r="K150" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="L150" t="n">
-        <v>5.86</v>
+        <v>5.96</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
-      </c>
-      <c r="N150" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.04</v>
+      </c>
       <c r="O150" t="n">
-        <v>0.368</v>
+        <v>0.421</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -18021,7 +17997,7 @@
         <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18033,35 +18009,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Terracciano F.</t>
+          <t>Sverko</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B;Dd;Ds</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F151" t="n">
         <v>4</v>
       </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -18069,25 +18045,23 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K151" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L151" t="n">
         <v>5.86</v>
       </c>
-      <c r="L151" t="n">
-        <v>5.83</v>
-      </c>
       <c r="M151" t="n">
-        <v>3</v>
-      </c>
-      <c r="N151" t="n">
-        <v>0.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="n">
-        <v>0.535</v>
+        <v>0.368</v>
       </c>
       <c r="P151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -18108,7 +18082,7 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X151" t="n">
         <v>0</v>
@@ -18120,24 +18094,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Biraghi</t>
+          <t>Terracciano F.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>B;Dd;Ds</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F152" t="n">
         <v>2</v>
@@ -18148,7 +18122,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -18156,25 +18130,25 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K152" t="n">
-        <v>5.59</v>
+        <v>5.86</v>
       </c>
       <c r="L152" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="M152" t="n">
         <v>3</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="O152" t="n">
-        <v>0.526</v>
+        <v>0.535</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
@@ -18195,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X152" t="n">
         <v>0</v>
@@ -18207,17 +18181,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Lazzari</t>
+          <t>Biraghi</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -18235,7 +18209,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>32</v>
+        <v>35.2</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -18243,22 +18217,22 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K153" t="n">
-        <v>5.79</v>
+        <v>5.59</v>
       </c>
       <c r="L153" t="n">
-        <v>5.74</v>
+        <v>5.59</v>
       </c>
       <c r="M153" t="n">
         <v>3</v>
       </c>
       <c r="N153" t="n">
-        <v>-0.13</v>
+        <v>-0.36</v>
       </c>
       <c r="O153" t="n">
-        <v>0.553</v>
+        <v>0.526</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -18282,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X153" t="n">
         <v>0</v>
@@ -18294,21 +18268,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sabelli</t>
+          <t>Lazzari</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>5</v>
@@ -18322,30 +18296,30 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>5.81</v>
+        <v>5.79</v>
       </c>
       <c r="L154" t="n">
-        <v>5.65</v>
+        <v>5.74</v>
       </c>
       <c r="M154" t="n">
         <v>3</v>
       </c>
       <c r="N154" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="O154" t="n">
-        <v>0.649</v>
+        <v>0.553</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -18357,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -18369,7 +18343,7 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X154" t="n">
         <v>0</v>
@@ -18381,21 +18355,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ebosse</t>
+          <t>Sabelli</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>5</v>
@@ -18409,7 +18383,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -18417,38 +18391,38 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K155" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="L155" t="n">
-        <v>5.72</v>
+        <v>5.65</v>
       </c>
       <c r="M155" t="n">
         <v>3</v>
       </c>
       <c r="N155" t="n">
-        <v>2.44</v>
+        <v>-0.24</v>
       </c>
       <c r="O155" t="n">
-        <v>0.158</v>
+        <v>0.649</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
       <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
         <v>5</v>
       </c>
-      <c r="T155" t="n">
-        <v>5.6</v>
-      </c>
       <c r="U155" t="n">
         <v>0</v>
       </c>
@@ -18456,7 +18430,7 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -18468,24 +18442,24 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Marianucci</t>
+          <t>Ebosse</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F156" t="n">
         <v>2</v>
@@ -18496,30 +18470,30 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>25.8</v>
+        <v>28.1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Affare</t>
+          <t>Equo</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K156" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="L156" t="n">
-        <v>5.73</v>
+        <v>5.72</v>
       </c>
       <c r="M156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O156" t="n">
-        <v>0.316</v>
+        <v>0.158</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -18531,10 +18505,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -18543,7 +18517,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -18555,7 +18529,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Rugani</t>
+          <t>Marianucci</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18565,7 +18539,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -18583,7 +18557,7 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -18591,28 +18565,28 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K157" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
       <c r="L157" t="n">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
       <c r="M157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N157" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>0.193</v>
+        <v>0.316</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -18642,7 +18616,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ziolkowski</t>
+          <t>Rugani</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18652,17 +18626,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D158" t="n">
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
@@ -18670,28 +18644,30 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>21.4</v>
+        <v>25.4</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K158" t="n">
-        <v>5.94</v>
+        <v>5.69</v>
       </c>
       <c r="L158" t="n">
-        <v>5.78</v>
+        <v>5.56</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
-      </c>
-      <c r="N158" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N158" t="n">
+        <v>3.14</v>
+      </c>
       <c r="O158" t="n">
-        <v>0.237</v>
+        <v>0.193</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -18715,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X158" t="n">
         <v>0</v>
@@ -18727,35 +18703,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Candè</t>
+          <t>Ziolkowski</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
+        <v>7</v>
+      </c>
+      <c r="F159" t="n">
         <v>4</v>
       </c>
-      <c r="F159" t="n">
-        <v>2</v>
-      </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
           <t>Low Cost</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>18.9</v>
+        <v>21.4</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -18763,22 +18739,20 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K159" t="n">
-        <v>5.69</v>
+        <v>5.94</v>
       </c>
       <c r="L159" t="n">
-        <v>5.56</v>
+        <v>5.78</v>
       </c>
       <c r="M159" t="n">
-        <v>2</v>
-      </c>
-      <c r="N159" t="n">
-        <v>-0.26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="n">
-        <v>0.329</v>
+        <v>0.237</v>
       </c>
       <c r="P159" t="n">
         <v>0</v>
@@ -18802,7 +18776,7 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X159" t="n">
         <v>0</v>
@@ -18814,17 +18788,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Casale</t>
+          <t>Candè</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -18842,7 +18816,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -18850,22 +18824,22 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K160" t="n">
-        <v>5.65</v>
+        <v>5.69</v>
       </c>
       <c r="L160" t="n">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="M160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N160" t="n">
-        <v>0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="O160" t="n">
-        <v>0.386</v>
+        <v>0.329</v>
       </c>
       <c r="P160" t="n">
         <v>0</v>
@@ -18889,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X160" t="n">
         <v>0</v>
@@ -18901,7 +18875,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Casale</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -18911,11 +18885,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
         <v>4</v>
@@ -18929,7 +18903,7 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -18937,22 +18911,22 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K161" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="L161" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N161" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="O161" t="n">
-        <v>0.303</v>
+        <v>0.386</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -18976,7 +18950,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -18988,58 +18962,58 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Goglichidze</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
         <v>5</v>
       </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>6</v>
-      </c>
       <c r="K162" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="L162" t="n">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
-        <v>2.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O162" t="n">
-        <v>0.342</v>
+        <v>0.303</v>
       </c>
       <c r="P162" t="n">
         <v>0</v>
@@ -19063,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
@@ -19075,56 +19049,58 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Moreno M.</t>
+          <t>Goglichidze</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
+        <v>5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
         <v>6</v>
       </c>
-      <c r="F163" t="n">
-        <v>3</v>
-      </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Equo</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
       <c r="K163" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="L163" t="n">
-        <v>5.67</v>
+        <v>5.58</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2.01</v>
+      </c>
       <c r="O163" t="n">
-        <v>0.079</v>
+        <v>0.342</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -19136,10 +19112,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -19148,7 +19124,7 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X163" t="n">
         <v>0</v>
@@ -19160,27 +19136,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ndaba</t>
+          <t>Moreno M.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
@@ -19188,7 +19164,7 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>15.8</v>
+        <v>16.6</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -19196,20 +19172,20 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L164" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M164" t="n">
         <v>1</v>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -19221,10 +19197,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T164" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -19245,27 +19221,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Odenthal</t>
+          <t>Ndaba</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
@@ -19273,7 +19249,7 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>11</v>
+        <v>15.8</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -19281,20 +19257,20 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M165" t="n">
         <v>1</v>
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -19306,13 +19282,13 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T165" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="U165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -19330,27 +19306,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Otoa</t>
+          <t>Carboni F.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
@@ -19358,7 +19334,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>11</v>
+        <v>14.2</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -19366,22 +19342,22 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L166" t="n">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="M166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N166" t="n">
-        <v>0.68</v>
+        <v>2.44</v>
       </c>
       <c r="O166" t="n">
-        <v>0.171</v>
+        <v>0.061</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -19393,10 +19369,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -19405,7 +19381,7 @@
         <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X166" t="n">
         <v>0</v>
@@ -19417,27 +19393,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sagrado</t>
+          <t>Odenthal</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>3</v>
       </c>
       <c r="E167" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
@@ -19445,7 +19421,7 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -19453,20 +19429,20 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>1</v>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -19478,10 +19454,10 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T167" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="U167" t="n">
         <v>1</v>
@@ -19490,7 +19466,7 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
@@ -19502,7 +19478,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kofler</t>
+          <t>Otoa</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -19512,50 +19488,76 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>7</v>
+      </c>
+      <c r="F168" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>11</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>10</v>
+      </c>
+      <c r="K168" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L168" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>2</v>
+      </c>
+      <c r="T168" t="n">
         <v>5</v>
       </c>
-      <c r="E168" t="n">
-        <v>3</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" s="6" t="inlineStr">
-        <is>
-          <t>Low Cost</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="n">
-        <v>2</v>
-      </c>
-      <c r="T168" t="n">
-        <v>6</v>
-      </c>
       <c r="U168" t="n">
         <v>0</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
       </c>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
+      <c r="W168" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="inlineStr"/>
       <c r="AA168" t="inlineStr"/>
@@ -19563,7 +19565,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bakoune</t>
+          <t>Sagrado</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -19573,11 +19575,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E169" t="n">
         <v>4</v>
@@ -19590,33 +19592,57 @@
           <t>Low Cost</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Equo</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L169" t="n">
+        <v>5.33</v>
+      </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
+      <c r="O169" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
       <c r="S169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T169" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
       </c>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
+      <c r="W169" t="n">
+        <v>1</v>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr"/>
@@ -19624,24 +19650,24 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Terzic</t>
+          <t>Kofler</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E170" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F170" t="n">
         <v>2</v>
@@ -19668,7 +19694,7 @@
         <v>2</v>
       </c>
       <c r="T170" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -19685,27 +19711,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mitaj</t>
+          <t>Bakoune</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F171" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
@@ -19726,10 +19752,10 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -19746,7 +19772,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Alhassane</t>
+          <t>Terzic</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19756,17 +19782,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
@@ -19807,27 +19833,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Akpoguma</t>
+          <t>Alhassane</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
@@ -19848,10 +19874,10 @@
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U173" t="n">
         <v>0</v>
@@ -19868,24 +19894,24 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Puczka</t>
+          <t>Akpoguma</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F174" t="n">
         <v>2</v>
@@ -19909,10 +19935,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -19929,27 +19955,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Halhal</t>
+          <t>Puczka</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
@@ -19970,10 +19996,10 @@
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T175" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -19990,12 +20016,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Franjic</t>
+          <t>Halhal</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B;Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -20007,10 +20033,10 @@
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
@@ -20034,7 +20060,7 @@
         <v>2</v>
       </c>
       <c r="T176" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20051,17 +20077,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Tchato</t>
+          <t>Franjic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>B;Ds;E</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -20092,10 +20118,10 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U177" t="n">
         <v>0</v>
@@ -20112,27 +20138,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Tchato</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dd;Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
@@ -20173,24 +20199,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Drameh</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dd;Ds;E</t>
+          <t>Dd;Dc</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F179" t="n">
         <v>2</v>
@@ -20234,24 +20260,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Diawara S.</t>
+          <t>Drameh</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ds;Dc</t>
+          <t>Dd;Ds;E</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F180" t="n">
         <v>2</v>
@@ -20295,17 +20321,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Aurelio</t>
+          <t>Diawara S.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Ds;Dc</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20356,68 +20382,46 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Dembelè A.</t>
+          <t>Aurelio</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dd;E</t>
+          <t>Ds;E</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>Scommessa</t>
-        </is>
-      </c>
-      <c r="H182" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Affare</t>
-        </is>
-      </c>
-      <c r="J182" t="n">
-        <v>1</v>
-      </c>
-      <c r="K182" t="n">
-        <v>5</v>
-      </c>
-      <c r="L182" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Low Cost</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="n">
-        <v>2</v>
-      </c>
-      <c r="N182" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
       <c r="S182" t="n">
         <v>0</v>
       </c>
@@ -20430,12 +20434,8 @@
       <c r="V182" t="n">
         <v>0</v>
       </c>
-      <c r="W182" t="n">
-        <v>0</v>
-      </c>
-      <c r="X182" t="n">
-        <v>0</v>
-      </c>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
@@ -20443,24 +20443,24 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Goldaniga</t>
+          <t>Dembelè A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dc</t>
+          <t>Dd;E</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="D183" t="n">
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" t="n">
         <v>1</v>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>27</v>
+        <v>43.6</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -20479,22 +20479,22 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N183" t="n">
-        <v>-5.66</v>
+        <v>-0.89</v>
       </c>
       <c r="O183" t="n">
-        <v>0.377</v>
+        <v>0.132</v>
       </c>
       <c r="P183" t="n">
         <v>0</v>
@@ -20530,27 +20530,27 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Carboni F.</t>
+          <t>Goldaniga</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ds;E</t>
+          <t>Dc</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
@@ -20558,30 +20558,30 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>14.2</v>
+        <v>27</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
         <v>3</v>
       </c>
       <c r="N184" t="n">
-        <v>2.44</v>
+        <v>-5.66</v>
       </c>
       <c r="O184" t="n">
-        <v>0.061</v>
+        <v>0.377</v>
       </c>
       <c r="P184" t="n">
         <v>0</v>
@@ -21113,8 +21113,69 @@
       <c r="Z191" t="inlineStr"/>
       <c r="AA191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Obric</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Dc</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Scommessa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA191"/>
+  <autoFilter ref="A1:AA192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -24572,10 +24572,10 @@
         <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Equo</t>
+          <t>Affare</t>
         </is>
       </c>
       <c r="J41" t="n">

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
         <v>5</v>
@@ -965,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1809,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>5.58</v>
+        <v>5.36</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T24" t="n">
         <v>4</v>
@@ -6020,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -6366,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -6688,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -6775,10 +6775,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -6862,10 +6862,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -6949,10 +6949,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>6.17</v>
+        <v>6.07</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7210,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>5.9</v>
+        <v>5.92</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7382,10 +7382,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7556,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -7643,16 +7643,16 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>7.75</v>
+        <v>8.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
         <v>6</v>
@@ -7730,16 +7730,16 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
         <v>6</v>
@@ -8707,7 +8707,7 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
         <v>6.5</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -9136,10 +9136,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="U40" t="n">
         <v>1</v>
@@ -9310,10 +9310,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -10263,10 +10263,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="U53" t="n">
         <v>2</v>
@@ -11042,10 +11042,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T62" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -11386,10 +11386,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>6.58</v>
+        <v>6.36</v>
       </c>
       <c r="U66" t="n">
         <v>1</v>
@@ -11983,10 +11983,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T73" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -12238,10 +12238,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T76" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -12390,10 +12390,10 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T78" t="n">
-        <v>6.75</v>
+        <v>6.64</v>
       </c>
       <c r="U78" t="n">
         <v>1</v>
@@ -12573,10 +12573,10 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -12817,10 +12817,10 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T85" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -12939,13 +12939,13 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -13192,10 +13192,10 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T90" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -13540,10 +13540,10 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -13714,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T96" t="n">
         <v>6</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T102" t="n">
-        <v>5.62</v>
+        <v>5.8</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -15015,10 +15015,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T111" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -15707,10 +15707,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -16225,10 +16225,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T125" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -16310,10 +16310,10 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T126" t="n">
-        <v>5.67</v>
+        <v>5.79</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -16397,10 +16397,10 @@
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T127" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -16482,10 +16482,10 @@
         <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T128" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16567,10 +16567,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T129" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -16652,10 +16652,10 @@
         <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T130" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="U130" t="n">
         <v>2</v>
@@ -17133,7 +17133,7 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T137" t="n">
         <v>6</v>
@@ -17255,10 +17255,10 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T139" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -17621,10 +17621,10 @@
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T145" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -17702,7 +17702,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T146" t="n">
         <v>6</v>
@@ -19998,10 +19998,10 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T174" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -21270,10 +21270,10 @@
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U192" t="n">
         <v>0</v>
@@ -21769,10 +21769,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -21856,10 +21856,10 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U5" t="n">
         <v>3</v>
@@ -22550,16 +22550,16 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -22983,10 +22983,10 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>8.25</v>
+        <v>7.36</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -23244,10 +23244,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -23416,16 +23416,16 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>7.3</v>
+        <v>7.33</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>3</v>
@@ -23673,10 +23673,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -24191,10 +24191,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -24256,10 +24256,10 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>7.12</v>
+        <v>6.9</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -24439,16 +24439,16 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>7.08</v>
+        <v>7.71</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -24500,10 +24500,10 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -25197,13 +25197,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>5.67</v>
+        <v>6.21</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -25545,10 +25545,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T50" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>7.62</v>
+        <v>7.3</v>
       </c>
       <c r="U54" t="n">
         <v>2</v>
@@ -26152,10 +26152,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="U57" t="n">
         <v>1</v>
@@ -26846,10 +26846,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T65" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -27020,10 +27020,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T67" t="n">
-        <v>6.17</v>
+        <v>6.07</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -27107,10 +27107,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T68" t="n">
-        <v>6.58</v>
+        <v>6.43</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -27194,10 +27194,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T69" t="n">
-        <v>6.92</v>
+        <v>6.79</v>
       </c>
       <c r="U69" t="n">
         <v>1</v>
@@ -27801,7 +27801,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="n">
         <v>6.5</v>
@@ -27810,7 +27810,7 @@
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" t="n">
         <v>0</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" t="n">
         <v>6.5</v>
@@ -29240,7 +29240,7 @@
         <v>2</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T95" t="n">
         <v>6</v>
@@ -29588,10 +29588,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T99" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -29675,10 +29675,10 @@
         <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T100" t="n">
-        <v>6.75</v>
+        <v>6.57</v>
       </c>
       <c r="U100" t="n">
         <v>1</v>
@@ -30108,10 +30108,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -30369,13 +30369,13 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T108" t="n">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -30456,10 +30456,10 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T109" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -30717,10 +30717,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T112" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -30802,10 +30802,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T113" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -31148,10 +31148,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T117" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -31233,10 +31233,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T118" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -31407,10 +31407,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T120" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="U120" t="n">
         <v>1</v>
@@ -31579,16 +31579,16 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" t="n">
         <v>3</v>
@@ -31840,10 +31840,10 @@
         <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T125" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T129" t="n">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -33963,10 +33963,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T152" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -34137,10 +34137,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T154" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -34746,10 +34746,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T161" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="U161" t="n">
         <v>0</v>
@@ -36471,7 +36471,7 @@
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T184" t="n">
         <v>5.5</v>
@@ -37680,13 +37680,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
@@ -37765,10 +37765,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>7.17</v>
+        <v>7.07</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -38259,13 +38259,13 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>6.5</v>
+        <v>7.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -38431,10 +38431,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -38518,10 +38518,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>7.5</v>
+        <v>7.36</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -39186,10 +39186,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>6.42</v>
+        <v>6.29</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -39273,7 +39273,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
         <v>7.5</v>
@@ -39282,7 +39282,7 @@
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
         <v>6</v>
@@ -39534,10 +39534,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>6.67</v>
+        <v>6.38</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
@@ -39621,13 +39621,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -39967,10 +39967,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -40054,10 +40054,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -40226,10 +40226,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -40398,10 +40398,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -40483,10 +40483,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="U36" t="n">
         <v>3</v>
@@ -40655,13 +40655,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>8.25</v>
+        <v>9.57</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -40842,10 +40842,10 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>8.300000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="U41" t="n">
         <v>3</v>
@@ -40903,13 +40903,13 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>6.08</v>
+        <v>6.64</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -41073,13 +41073,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -41506,7 +41506,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="n">
         <v>5.5</v>
@@ -41678,10 +41678,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="n">
-        <v>5.7</v>
+        <v>5.58</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -42020,10 +42020,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="U55" t="n">
         <v>1</v>
@@ -42856,10 +42856,10 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -42917,10 +42917,10 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>10</v>
+        <v>7.75</v>
       </c>
       <c r="U68" t="n">
         <v>1</v>
@@ -43085,10 +43085,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>

--- a/export/lista_asta.xlsx
+++ b/export/lista_asta.xlsx
@@ -965,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>5.25</v>
+        <v>4.94</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1809,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1959,10 +1959,10 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -3056,10 +3056,10 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -6107,10 +6107,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -6279,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>6.75</v>
+        <v>6.64</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -6540,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>7.43</v>
+        <v>7.31</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7667,10 +7667,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -7752,13 +7752,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>6.69</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -7926,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>7.2</v>
+        <v>7.08</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -8731,16 +8731,16 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>5.93</v>
+        <v>6.12</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -8988,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -9508,10 +9508,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>5.62</v>
+        <v>5.5</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -9595,10 +9595,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10983,16 +10983,16 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>5.56</v>
+        <v>5.67</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" t="n">
         <v>8</v>
@@ -11070,10 +11070,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T62" t="n">
-        <v>6.21</v>
+        <v>6.12</v>
       </c>
       <c r="U62" t="n">
         <v>1</v>
@@ -11501,10 +11501,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="n">
-        <v>6.31</v>
+        <v>6.22</v>
       </c>
       <c r="U67" t="n">
         <v>1</v>
@@ -11586,13 +11586,13 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T68" t="n">
-        <v>5.81</v>
+        <v>6.28</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -11671,10 +11671,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T69" t="n">
-        <v>5.69</v>
+        <v>5.61</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -12100,10 +12100,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -12753,10 +12753,10 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="n">
-        <v>6.1</v>
+        <v>5.67</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -12875,16 +12875,16 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
@@ -12936,10 +12936,10 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T86" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -14553,10 +14553,10 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T105" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -15848,16 +15848,16 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T120" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" t="n">
         <v>1</v>
@@ -16617,10 +16617,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="U129" t="n">
         <v>2</v>
@@ -16915,10 +16915,10 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T133" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -17159,10 +17159,10 @@
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="n">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T138" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T139" t="n">
         <v>6</v>
@@ -17586,16 +17586,16 @@
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T144" t="n">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr"/>
@@ -18679,7 +18679,7 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T157" t="n">
         <v>6</v>
@@ -19902,7 +19902,7 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T172" t="n">
         <v>5</v>
@@ -20828,10 +20828,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T186" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="U186" t="n">
         <v>0</v>
@@ -21595,16 +21595,16 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>7.43</v>
+        <v>7.94</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>5</v>
@@ -22115,13 +22115,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>6.79</v>
+        <v>7.19</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -22202,16 +22202,16 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>6.88</v>
+        <v>7.17</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -22289,10 +22289,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>7.56</v>
+        <v>7.06</v>
       </c>
       <c r="U10" t="n">
         <v>3</v>
@@ -22376,10 +22376,10 @@
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -22463,10 +22463,10 @@
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -23760,16 +23760,16 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>7.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -23932,16 +23932,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>6.62</v>
+        <v>7.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
         <v>5</v>
@@ -24430,13 +24430,13 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>6.75</v>
+        <v>7.29</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25249,10 +25249,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="n">
-        <v>6.21</v>
+        <v>5.94</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
@@ -25336,10 +25336,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T47" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -25597,10 +25597,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -25858,13 +25858,13 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -27679,10 +27679,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T74" t="n">
-        <v>6.36</v>
+        <v>6.25</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -27764,10 +27764,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -28175,10 +28175,10 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="n">
-        <v>6.62</v>
+        <v>6.5</v>
       </c>
       <c r="U80" t="n">
         <v>1</v>
@@ -28419,10 +28419,10 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T84" t="n">
-        <v>6.75</v>
+        <v>6.57</v>
       </c>
       <c r="U84" t="n">
         <v>1</v>
@@ -28480,10 +28480,10 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -28541,16 +28541,16 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>6.67</v>
+        <v>6.79</v>
       </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
@@ -29527,10 +29527,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" t="n">
-        <v>6.7</v>
+        <v>6.58</v>
       </c>
       <c r="U98" t="n">
         <v>1</v>
@@ -29612,10 +29612,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T99" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -29873,7 +29873,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T102" t="n">
         <v>6</v>
@@ -30306,10 +30306,10 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T107" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -31431,10 +31431,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T120" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -31951,7 +31951,7 @@
         <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T126" t="n">
         <v>6</v>
@@ -32210,10 +32210,10 @@
         <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T129" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -32469,10 +32469,10 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T132" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -34052,16 +34052,16 @@
         <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T153" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="U153" t="n">
         <v>1</v>
       </c>
       <c r="V153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" t="n">
         <v>0</v>
@@ -34226,10 +34226,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T155" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -34831,10 +34831,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T162" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -37850,13 +37850,13 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="U5" t="n">
         <v>7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
@@ -38259,10 +38259,10 @@
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>6.79</v>
+        <v>6.5</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -38346,10 +38346,10 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>8.25</v>
+        <v>7.94</v>
       </c>
       <c r="U11" t="n">
         <v>5</v>
@@ -38518,10 +38518,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="U13" t="n">
         <v>3</v>
@@ -38951,10 +38951,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -39186,10 +39186,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>6.19</v>
+        <v>6.11</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -39273,13 +39273,13 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
@@ -39360,10 +39360,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
@@ -39447,13 +39447,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T24" t="n">
-        <v>8.08</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -39708,10 +39708,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>6.75</v>
+        <v>6.57</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
@@ -40056,13 +40056,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>7.75</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
         <v>2</v>
@@ -40230,13 +40230,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>7.69</v>
+        <v>7.94</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -41591,10 +41591,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="U50" t="n">
         <v>1</v>
@@ -41765,13 +41765,13 @@
         <v>3</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -42022,10 +42022,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>6.69</v>
+        <v>6.61</v>
       </c>
       <c r="U55" t="n">
         <v>1</v>
@@ -42366,10 +42366,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="n">
-        <v>7.4</v>
+        <v>7.08</v>
       </c>
       <c r="U59" t="n">
         <v>2</v>
